--- a/deliverables/foglio_controllo_cedolini.xlsx
+++ b/deliverables/foglio_controllo_cedolini.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Contributo a carico del dipendente diverso da imponibile × aliquota. Priorità alta.</t>
+          <t>Contributo a carico del dipendente diverso da imponibile arrotondato all'euro × aliquota. Priorità alta.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D10" s="30" t="n">
-        <v>155.28</v>
+        <v>155.31</v>
       </c>
       <c r="E10" s="31">
         <f>Mese!AB5</f>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1310.02</v>
+        <v>1310</v>
       </c>
       <c r="E13" s="31">
         <f>Mese!AG5</f>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="D17" s="30" t="n">
-        <v>250.79</v>
+        <v>250.8</v>
       </c>
       <c r="E17" s="31">
         <f>Mese!AB11</f>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D20" s="30" t="n">
-        <v>1970.3</v>
+        <v>1970.29</v>
       </c>
       <c r="E20" s="31">
         <f>Mese!AG11</f>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="D24" s="30" t="n">
-        <v>132.77</v>
+        <v>132.8</v>
       </c>
       <c r="E24" s="31">
         <f>Mese!AB17</f>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="D27" s="30" t="n">
-        <v>1150.97</v>
+        <v>1150.95</v>
       </c>
       <c r="E27" s="31">
         <f>Mese!AG17</f>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D31" s="30" t="n">
-        <v>217.86</v>
+        <v>217.89</v>
       </c>
       <c r="E31" s="31">
         <f>Mese!AB23</f>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="D34" s="30" t="n">
-        <v>1752.11</v>
+        <v>1752.09</v>
       </c>
       <c r="E34" s="31">
         <f>Mese!AG23</f>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="D38" s="30" t="n">
-        <v>130.07</v>
+        <v>130.04</v>
       </c>
       <c r="E38" s="31">
         <f>Mese!AB29</f>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D41" s="30" t="n">
-        <v>1131.9</v>
+        <v>1131.92</v>
       </c>
       <c r="E41" s="31">
         <f>Mese!AG29</f>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="D45" s="30" t="n">
-        <v>86.34999999999999</v>
+        <v>86.39</v>
       </c>
       <c r="E45" s="31">
         <f>Mese!AB35</f>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>807.17</v>
+        <v>807.13</v>
       </c>
       <c r="E48" s="31">
         <f>Mese!AG35</f>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="D52" s="30" t="n">
-        <v>135.44</v>
+        <v>135.46</v>
       </c>
       <c r="E52" s="31">
         <f>Mese!AB41</f>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="D55" s="30" t="n">
-        <v>1169.83</v>
+        <v>1169.81</v>
       </c>
       <c r="E55" s="31">
         <f>Mese!AG41</f>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="D59" s="30" t="n">
-        <v>163.45</v>
+        <v>163.49</v>
       </c>
       <c r="E59" s="31">
         <f>Mese!AB47</f>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="D62" s="30" t="n">
-        <v>1367.75</v>
+        <v>1367.72</v>
       </c>
       <c r="E62" s="31">
         <f>Mese!AG47</f>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="D66" s="30" t="n">
-        <v>257.3</v>
+        <v>257.32</v>
       </c>
       <c r="E66" s="31">
         <f>Mese!AB53</f>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="D69" s="30" t="n">
-        <v>2009.9</v>
+        <v>2009.89</v>
       </c>
       <c r="E69" s="31">
         <f>Mese!AG53</f>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="D73" s="30" t="n">
-        <v>176.35</v>
+        <v>176.36</v>
       </c>
       <c r="E73" s="31">
         <f>Mese!AB59</f>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D76" s="30" t="n">
-        <v>1458.85</v>
+        <v>1458.84</v>
       </c>
       <c r="E76" s="31">
         <f>Mese!AG59</f>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="D80" s="30" t="n">
-        <v>136.59</v>
+        <v>136.56</v>
       </c>
       <c r="E80" s="31">
         <f>Mese!AB65</f>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D83" s="30" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="E83" s="31">
         <f>Mese!AG65</f>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="D87" s="30" t="n">
-        <v>136.59</v>
+        <v>136.56</v>
       </c>
       <c r="E87" s="31">
         <f>Mese!AB71</f>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="D90" s="30" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="E90" s="31">
         <f>Mese!AG71</f>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="D94" s="30" t="n">
-        <v>193.21</v>
+        <v>193.17</v>
       </c>
       <c r="E94" s="31">
         <f>Mese!AB77</f>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="D97" s="30" t="n">
-        <v>1577.94</v>
+        <v>1577.97</v>
       </c>
       <c r="E97" s="31">
         <f>Mese!AG77</f>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="D101" s="30" t="n">
-        <v>188.74</v>
+        <v>188.76</v>
       </c>
       <c r="E101" s="31">
         <f>Mese!AB83</f>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D104" s="30" t="n">
-        <v>1546.42</v>
+        <v>1546.41</v>
       </c>
       <c r="E104" s="31">
         <f>Mese!AG83</f>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="D108" s="30" t="n">
-        <v>87.44</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="E108" s="31">
         <f>Mese!AB89</f>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D111" s="30" t="n">
-        <v>815.28</v>
+        <v>815.24</v>
       </c>
       <c r="E111" s="31">
         <f>Mese!AG89</f>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D115" s="30" t="n">
-        <v>158.83</v>
+        <v>158.8</v>
       </c>
       <c r="E115" s="31">
         <f>Mese!AB95</f>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="D118" s="30" t="n">
-        <v>1335.1</v>
+        <v>1335.12</v>
       </c>
       <c r="E118" s="31">
         <f>Mese!AG95</f>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="D129" s="30" t="n">
-        <v>160.54</v>
+        <v>160.55</v>
       </c>
       <c r="E129" s="31">
         <f>Mese!AB107</f>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="D132" s="30" t="n">
-        <v>1347.2</v>
+        <v>1347.19</v>
       </c>
       <c r="E132" s="31">
         <f>Mese!AG107</f>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="D143" s="30" t="n">
-        <v>140.81</v>
+        <v>140.79</v>
       </c>
       <c r="E143" s="31">
         <f>Mese!AB119</f>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D146" s="30" t="n">
-        <v>1207.75</v>
+        <v>1207.76</v>
       </c>
       <c r="E146" s="31">
         <f>Mese!AG119</f>
@@ -13929,19 +13929,19 @@
         <v>1689.7</v>
       </c>
       <c r="O5" s="17" t="n">
-        <v>155.28</v>
+        <v>155.31</v>
       </c>
       <c r="P5" s="17" t="n">
-        <v>1534.42</v>
+        <v>1534.39</v>
       </c>
       <c r="Q5" s="17" t="n">
-        <v>201.38</v>
+        <v>201.37</v>
       </c>
       <c r="R5" s="17" t="n">
         <v>23.02</v>
       </c>
       <c r="S5" s="17" t="n">
-        <v>1347.52</v>
+        <v>1347.5</v>
       </c>
       <c r="T5" s="17" t="n">
         <v>146.02</v>
@@ -13972,7 +13972,7 @@
         <v/>
       </c>
       <c r="AB5" s="19">
-        <f>IF($A5="","",ROUND(N5*Parametri!$C$6,2))</f>
+        <f>IF($A5="","",ROUND(ROUND(N5,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC5" s="19">
@@ -14098,19 +14098,19 @@
         <v>2040.71</v>
       </c>
       <c r="O6" s="17" t="n">
-        <v>187.54</v>
+        <v>187.57</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>1853.17</v>
+        <v>1853.14</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>287.44</v>
+        <v>287.43</v>
       </c>
       <c r="R6" s="17" t="n">
         <v>27.8</v>
       </c>
       <c r="S6" s="17" t="n">
-        <v>1537.93</v>
+        <v>1537.91</v>
       </c>
       <c r="T6" s="17" t="n">
         <v>176.36</v>
@@ -14141,7 +14141,7 @@
         <v/>
       </c>
       <c r="AB6" s="19">
-        <f>IF($A6="","",ROUND(N6*Parametri!$C$6,2))</f>
+        <f>IF($A6="","",ROUND(ROUND(N6,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC6" s="19">
@@ -14267,19 +14267,19 @@
         <v>1981.68</v>
       </c>
       <c r="O7" s="17" t="n">
-        <v>188.06</v>
+        <v>188.09</v>
       </c>
       <c r="P7" s="17" t="n">
-        <v>1793.62</v>
+        <v>1793.59</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>271.36</v>
+        <v>271.35</v>
       </c>
       <c r="R7" s="17" t="n">
         <v>26.9</v>
       </c>
       <c r="S7" s="17" t="n">
-        <v>1495.36</v>
+        <v>1495.34</v>
       </c>
       <c r="T7" s="17" t="n">
         <v>171.26</v>
@@ -14310,7 +14310,7 @@
         <v/>
       </c>
       <c r="AB7" s="19">
-        <f>IF($A7="","",ROUND(N7*Parametri!$C$6,2))</f>
+        <f>IF($A7="","",ROUND(ROUND(N7,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC7" s="19">
@@ -14440,10 +14440,10 @@
         <v>2713.95</v>
       </c>
       <c r="O8" s="17" t="n">
-        <v>249.41</v>
+        <v>249.42</v>
       </c>
       <c r="P8" s="17" t="n">
-        <v>2464.54</v>
+        <v>2464.53</v>
       </c>
       <c r="Q8" s="17" t="n">
         <v>465.63</v>
@@ -14452,7 +14452,7 @@
         <v>36.97</v>
       </c>
       <c r="S8" s="17" t="n">
-        <v>1961.94</v>
+        <v>1961.93</v>
       </c>
       <c r="T8" s="17" t="n">
         <v>181.68</v>
@@ -14483,7 +14483,7 @@
         <v/>
       </c>
       <c r="AB8" s="19">
-        <f>IF($A8="","",ROUND(N8*Parametri!$C$6,2))</f>
+        <f>IF($A8="","",ROUND(ROUND(N8,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC8" s="19">
@@ -14609,10 +14609,10 @@
         <v>1529.41</v>
       </c>
       <c r="O9" s="17" t="n">
-        <v>140.55</v>
+        <v>140.52</v>
       </c>
       <c r="P9" s="17" t="n">
-        <v>1388.86</v>
+        <v>1388.89</v>
       </c>
       <c r="Q9" s="17" t="n">
         <v>162.08</v>
@@ -14621,7 +14621,7 @@
         <v>20.83</v>
       </c>
       <c r="S9" s="17" t="n">
-        <v>1205.95</v>
+        <v>1205.98</v>
       </c>
       <c r="T9" s="17" t="n">
         <v>132.17</v>
@@ -14652,7 +14652,7 @@
         <v/>
       </c>
       <c r="AB9" s="19">
-        <f>IF($A9="","",ROUND(N9*Parametri!$C$6,2))</f>
+        <f>IF($A9="","",ROUND(ROUND(N9,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC9" s="19">
@@ -14821,7 +14821,7 @@
         <v/>
       </c>
       <c r="AB10" s="19">
-        <f>IF($A10="","",ROUND(N10*Parametri!$C$6,2))</f>
+        <f>IF($A10="","",ROUND(ROUND(N10,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC10" s="19">
@@ -14947,10 +14947,10 @@
         <v>2728.91</v>
       </c>
       <c r="O11" s="17" t="n">
-        <v>250.79</v>
+        <v>250.8</v>
       </c>
       <c r="P11" s="17" t="n">
-        <v>2478.12</v>
+        <v>2478.11</v>
       </c>
       <c r="Q11" s="17" t="n">
         <v>470.65</v>
@@ -14959,7 +14959,7 @@
         <v>37.17</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>1970.3</v>
+        <v>1970.29</v>
       </c>
       <c r="T11" s="17" t="n">
         <v>235.83</v>
@@ -14990,7 +14990,7 @@
         <v/>
       </c>
       <c r="AB11" s="19">
-        <f>IF($A11="","",ROUND(N11*Parametri!$C$6,2))</f>
+        <f>IF($A11="","",ROUND(ROUND(N11,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC11" s="19">
@@ -15116,19 +15116,19 @@
         <v>2003.79</v>
       </c>
       <c r="O12" s="17" t="n">
-        <v>184.15</v>
+        <v>184.17</v>
       </c>
       <c r="P12" s="17" t="n">
-        <v>1819.64</v>
+        <v>1819.62</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>278.39</v>
+        <v>278.38</v>
       </c>
       <c r="R12" s="17" t="n">
         <v>27.29</v>
       </c>
       <c r="S12" s="17" t="n">
-        <v>1513.96</v>
+        <v>1513.95</v>
       </c>
       <c r="T12" s="17" t="n">
         <v>173.17</v>
@@ -15159,7 +15159,7 @@
         <v/>
       </c>
       <c r="AB12" s="19">
-        <f>IF($A12="","",ROUND(N12*Parametri!$C$6,2))</f>
+        <f>IF($A12="","",ROUND(ROUND(N12,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC12" s="19">
@@ -15285,19 +15285,19 @@
         <v>1688.35</v>
       </c>
       <c r="O13" s="17" t="n">
-        <v>155.16</v>
+        <v>155.13</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>1533.19</v>
+        <v>1533.22</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>201.04</v>
+        <v>201.05</v>
       </c>
       <c r="R13" s="17" t="n">
         <v>23</v>
       </c>
       <c r="S13" s="17" t="n">
-        <v>1309.15</v>
+        <v>1309.17</v>
       </c>
       <c r="T13" s="17" t="n">
         <v>145.91</v>
@@ -15328,7 +15328,7 @@
         <v/>
       </c>
       <c r="AB13" s="19">
-        <f>IF($A13="","",ROUND(N13*Parametri!$C$6,2))</f>
+        <f>IF($A13="","",ROUND(ROUND(N13,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC13" s="19">
@@ -15454,19 +15454,19 @@
         <v>1489.23</v>
       </c>
       <c r="O14" s="17" t="n">
-        <v>136.86</v>
+        <v>136.84</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>1352.37</v>
+        <v>1352.39</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>152.22</v>
+        <v>152.23</v>
       </c>
       <c r="R14" s="17" t="n">
         <v>20.29</v>
       </c>
       <c r="S14" s="17" t="n">
-        <v>1179.86</v>
+        <v>1179.87</v>
       </c>
       <c r="T14" s="17" t="n">
         <v>128.7</v>
@@ -15497,7 +15497,7 @@
         <v/>
       </c>
       <c r="AB14" s="19">
-        <f>IF($A14="","",ROUND(N14*Parametri!$C$6,2))</f>
+        <f>IF($A14="","",ROUND(ROUND(N14,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC14" s="19">
@@ -15623,19 +15623,19 @@
         <v>2143.66</v>
       </c>
       <c r="O15" s="17" t="n">
-        <v>197</v>
+        <v>197.03</v>
       </c>
       <c r="P15" s="17" t="n">
-        <v>1946.66</v>
+        <v>1946.63</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>312.68</v>
+        <v>312.67</v>
       </c>
       <c r="R15" s="17" t="n">
         <v>29.2</v>
       </c>
       <c r="S15" s="17" t="n">
-        <v>1604.78</v>
+        <v>1604.76</v>
       </c>
       <c r="T15" s="17" t="n">
         <v>185.25</v>
@@ -15666,7 +15666,7 @@
         <v/>
       </c>
       <c r="AB15" s="19">
-        <f>IF($A15="","",ROUND(N15*Parametri!$C$6,2))</f>
+        <f>IF($A15="","",ROUND(ROUND(N15,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC15" s="19">
@@ -15792,10 +15792,10 @@
         <v>1512.71</v>
       </c>
       <c r="O16" s="17" t="n">
-        <v>143.56</v>
+        <v>143.58</v>
       </c>
       <c r="P16" s="17" t="n">
-        <v>1369.15</v>
+        <v>1369.13</v>
       </c>
       <c r="Q16" s="17" t="n">
         <v>156.75</v>
@@ -15804,7 +15804,7 @@
         <v>20.54</v>
       </c>
       <c r="S16" s="17" t="n">
-        <v>1191.86</v>
+        <v>1191.84</v>
       </c>
       <c r="T16" s="17" t="n">
         <v>130.73</v>
@@ -15835,7 +15835,7 @@
         <v/>
       </c>
       <c r="AB16" s="19">
-        <f>IF($A16="","",ROUND(N16*Parametri!$C$6,2))</f>
+        <f>IF($A16="","",ROUND(ROUND(N16,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC16" s="19">
@@ -15961,19 +15961,19 @@
         <v>1444.73</v>
       </c>
       <c r="O17" s="17" t="n">
-        <v>132.77</v>
+        <v>132.8</v>
       </c>
       <c r="P17" s="17" t="n">
-        <v>1311.96</v>
+        <v>1311.93</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>141.31</v>
+        <v>141.3</v>
       </c>
       <c r="R17" s="17" t="n">
         <v>19.68</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>1150.97</v>
+        <v>1150.95</v>
       </c>
       <c r="T17" s="17" t="n">
         <v>124.85</v>
@@ -16004,7 +16004,7 @@
         <v/>
       </c>
       <c r="AB17" s="19">
-        <f>IF($A17="","",ROUND(N17*Parametri!$C$6,2))</f>
+        <f>IF($A17="","",ROUND(ROUND(N17,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC17" s="19">
@@ -16130,19 +16130,19 @@
         <v>2017.27</v>
       </c>
       <c r="O18" s="17" t="n">
-        <v>185.39</v>
+        <v>185.36</v>
       </c>
       <c r="P18" s="17" t="n">
-        <v>1831.88</v>
+        <v>1831.91</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>281.69</v>
+        <v>281.7</v>
       </c>
       <c r="R18" s="17" t="n">
         <v>27.48</v>
       </c>
       <c r="S18" s="17" t="n">
-        <v>1522.71</v>
+        <v>1522.73</v>
       </c>
       <c r="T18" s="17" t="n">
         <v>174.33</v>
@@ -16173,7 +16173,7 @@
         <v/>
       </c>
       <c r="AB18" s="19">
-        <f>IF($A18="","",ROUND(N18*Parametri!$C$6,2))</f>
+        <f>IF($A18="","",ROUND(ROUND(N18,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC18" s="19">
@@ -16299,19 +16299,19 @@
         <v>1681.19</v>
       </c>
       <c r="O19" s="17" t="n">
-        <v>154.5</v>
+        <v>154.48</v>
       </c>
       <c r="P19" s="17" t="n">
-        <v>1526.69</v>
+        <v>1526.71</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>199.29</v>
+        <v>199.3</v>
       </c>
       <c r="R19" s="17" t="n">
         <v>22.9</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>1304.5</v>
+        <v>1304.51</v>
       </c>
       <c r="T19" s="17" t="n">
         <v>145.29</v>
@@ -16342,7 +16342,7 @@
         <v/>
       </c>
       <c r="AB19" s="19">
-        <f>IF($A19="","",ROUND(N19*Parametri!$C$6,2))</f>
+        <f>IF($A19="","",ROUND(ROUND(N19,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC19" s="19">
@@ -16511,7 +16511,7 @@
         <v/>
       </c>
       <c r="AB20" s="19">
-        <f>IF($A20="","",ROUND(N20*Parametri!$C$6,2))</f>
+        <f>IF($A20="","",ROUND(ROUND(N20,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC20" s="19">
@@ -16637,10 +16637,10 @@
         <v>1336.26</v>
       </c>
       <c r="O21" s="17" t="n">
-        <v>122.8</v>
+        <v>122.78</v>
       </c>
       <c r="P21" s="17" t="n">
-        <v>1213.46</v>
+        <v>1213.48</v>
       </c>
       <c r="Q21" s="17" t="n">
         <v>116.18</v>
@@ -16649,7 +16649,7 @@
         <v>18.2</v>
       </c>
       <c r="S21" s="17" t="n">
-        <v>1079.08</v>
+        <v>1079.1</v>
       </c>
       <c r="T21" s="17" t="n">
         <v>115.48</v>
@@ -16680,7 +16680,7 @@
         <v/>
       </c>
       <c r="AB21" s="19">
-        <f>IF($A21="","",ROUND(N21*Parametri!$C$6,2))</f>
+        <f>IF($A21="","",ROUND(ROUND(N21,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC21" s="19">
@@ -16806,10 +16806,10 @@
         <v>2061.84</v>
       </c>
       <c r="O22" s="17" t="n">
-        <v>189.48</v>
+        <v>189.5</v>
       </c>
       <c r="P22" s="17" t="n">
-        <v>1872.36</v>
+        <v>1872.34</v>
       </c>
       <c r="Q22" s="17" t="n">
         <v>292.62</v>
@@ -16818,7 +16818,7 @@
         <v>28.09</v>
       </c>
       <c r="S22" s="17" t="n">
-        <v>1551.65</v>
+        <v>1551.63</v>
       </c>
       <c r="T22" s="17" t="n">
         <v>178.18</v>
@@ -16849,7 +16849,7 @@
         <v/>
       </c>
       <c r="AB22" s="19">
-        <f>IF($A22="","",ROUND(N22*Parametri!$C$6,2))</f>
+        <f>IF($A22="","",ROUND(ROUND(N22,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC22" s="19">
@@ -16975,19 +16975,19 @@
         <v>2370.58</v>
       </c>
       <c r="O23" s="17" t="n">
-        <v>217.86</v>
+        <v>217.89</v>
       </c>
       <c r="P23" s="17" t="n">
-        <v>2152.72</v>
+        <v>2152.69</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>368.32</v>
+        <v>368.31</v>
       </c>
       <c r="R23" s="17" t="n">
         <v>32.29</v>
       </c>
       <c r="S23" s="17" t="n">
-        <v>1752.11</v>
+        <v>1752.09</v>
       </c>
       <c r="T23" s="17" t="n">
         <v>204.86</v>
@@ -17018,7 +17018,7 @@
         <v/>
       </c>
       <c r="AB23" s="19">
-        <f>IF($A23="","",ROUND(N23*Parametri!$C$6,2))</f>
+        <f>IF($A23="","",ROUND(ROUND(N23,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC23" s="19">
@@ -17144,19 +17144,19 @@
         <v>2727.63</v>
       </c>
       <c r="O24" s="17" t="n">
-        <v>250.67</v>
+        <v>250.7</v>
       </c>
       <c r="P24" s="17" t="n">
-        <v>2476.96</v>
+        <v>2476.93</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>470.23</v>
+        <v>470.21</v>
       </c>
       <c r="R24" s="17" t="n">
         <v>37.15</v>
       </c>
       <c r="S24" s="17" t="n">
-        <v>1969.58</v>
+        <v>1969.57</v>
       </c>
       <c r="T24" s="17" t="n">
         <v>235.72</v>
@@ -17187,7 +17187,7 @@
         <v/>
       </c>
       <c r="AB24" s="19">
-        <f>IF($A24="","",ROUND(N24*Parametri!$C$6,2))</f>
+        <f>IF($A24="","",ROUND(ROUND(N24,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC24" s="19">
@@ -17317,19 +17317,19 @@
         <v>2839.85</v>
       </c>
       <c r="O25" s="17" t="n">
-        <v>260.98</v>
+        <v>261</v>
       </c>
       <c r="P25" s="17" t="n">
-        <v>2578.87</v>
+        <v>2578.85</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>507.93</v>
+        <v>507.92</v>
       </c>
       <c r="R25" s="17" t="n">
         <v>38.68</v>
       </c>
       <c r="S25" s="17" t="n">
-        <v>2032.26</v>
+        <v>2032.25</v>
       </c>
       <c r="T25" s="17" t="n">
         <v>168.72</v>
@@ -17360,7 +17360,7 @@
         <v/>
       </c>
       <c r="AB25" s="19">
-        <f>IF($A25="","",ROUND(N25*Parametri!$C$6,2))</f>
+        <f>IF($A25="","",ROUND(ROUND(N25,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC25" s="19">
@@ -17486,19 +17486,19 @@
         <v>1981.84</v>
       </c>
       <c r="O26" s="17" t="n">
-        <v>182.13</v>
+        <v>182.15</v>
       </c>
       <c r="P26" s="17" t="n">
-        <v>1799.71</v>
+        <v>1799.69</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>273.01</v>
+        <v>273</v>
       </c>
       <c r="R26" s="17" t="n">
         <v>27</v>
       </c>
       <c r="S26" s="17" t="n">
-        <v>1499.7</v>
+        <v>1499.69</v>
       </c>
       <c r="T26" s="17" t="n">
         <v>171.27</v>
@@ -17529,7 +17529,7 @@
         <v/>
       </c>
       <c r="AB26" s="19">
-        <f>IF($A26="","",ROUND(N26*Parametri!$C$6,2))</f>
+        <f>IF($A26="","",ROUND(ROUND(N26,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC26" s="19">
@@ -17655,19 +17655,19 @@
         <v>2490.58</v>
       </c>
       <c r="O27" s="17" t="n">
-        <v>228.88</v>
+        <v>228.92</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>2261.7</v>
+        <v>2261.66</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>397.74</v>
+        <v>397.73</v>
       </c>
       <c r="R27" s="17" t="n">
-        <v>33.93</v>
+        <v>33.92</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>1830.03</v>
+        <v>1830.01</v>
       </c>
       <c r="T27" s="17" t="n">
         <v>215.24</v>
@@ -17698,7 +17698,7 @@
         <v/>
       </c>
       <c r="AB27" s="19">
-        <f>IF($A27="","",ROUND(N27*Parametri!$C$6,2))</f>
+        <f>IF($A27="","",ROUND(ROUND(N27,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC27" s="19">
@@ -17824,19 +17824,19 @@
         <v>1698.61</v>
       </c>
       <c r="O28" s="17" t="n">
-        <v>156.1</v>
+        <v>156.14</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>1542.51</v>
+        <v>1542.47</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>203.56</v>
+        <v>203.55</v>
       </c>
       <c r="R28" s="17" t="n">
         <v>23.14</v>
       </c>
       <c r="S28" s="17" t="n">
-        <v>1315.81</v>
+        <v>1315.78</v>
       </c>
       <c r="T28" s="17" t="n">
         <v>146.79</v>
@@ -17867,7 +17867,7 @@
         <v/>
       </c>
       <c r="AB28" s="19">
-        <f>IF($A28="","",ROUND(N28*Parametri!$C$6,2))</f>
+        <f>IF($A28="","",ROUND(ROUND(N28,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC28" s="19">
@@ -17993,19 +17993,19 @@
         <v>1415.36</v>
       </c>
       <c r="O29" s="17" t="n">
-        <v>130.07</v>
+        <v>130.04</v>
       </c>
       <c r="P29" s="17" t="n">
-        <v>1285.29</v>
+        <v>1285.32</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>134.11</v>
+        <v>134.12</v>
       </c>
       <c r="R29" s="17" t="n">
         <v>19.28</v>
       </c>
       <c r="S29" s="17" t="n">
-        <v>1131.9</v>
+        <v>1131.92</v>
       </c>
       <c r="T29" s="17" t="n">
         <v>122.32</v>
@@ -18036,7 +18036,7 @@
         <v/>
       </c>
       <c r="AB29" s="19">
-        <f>IF($A29="","",ROUND(N29*Parametri!$C$6,2))</f>
+        <f>IF($A29="","",ROUND(ROUND(N29,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC29" s="19">
@@ -18162,19 +18162,19 @@
         <v>2628.59</v>
       </c>
       <c r="O30" s="17" t="n">
-        <v>241.57</v>
+        <v>241.61</v>
       </c>
       <c r="P30" s="17" t="n">
-        <v>2387.02</v>
+        <v>2386.98</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>436.95</v>
+        <v>436.93</v>
       </c>
       <c r="R30" s="17" t="n">
-        <v>35.81</v>
+        <v>35.8</v>
       </c>
       <c r="S30" s="17" t="n">
-        <v>1914.26</v>
+        <v>1914.25</v>
       </c>
       <c r="T30" s="17" t="n">
         <v>227.16</v>
@@ -18205,7 +18205,7 @@
         <v/>
       </c>
       <c r="AB30" s="19">
-        <f>IF($A30="","",ROUND(N30*Parametri!$C$6,2))</f>
+        <f>IF($A30="","",ROUND(ROUND(N30,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC30" s="19">
@@ -18331,10 +18331,10 @@
         <v>1642.23</v>
       </c>
       <c r="O31" s="17" t="n">
-        <v>150.92</v>
+        <v>150.9</v>
       </c>
       <c r="P31" s="17" t="n">
-        <v>1491.31</v>
+        <v>1491.33</v>
       </c>
       <c r="Q31" s="17" t="n">
         <v>189.74</v>
@@ -18343,7 +18343,7 @@
         <v>22.37</v>
       </c>
       <c r="S31" s="17" t="n">
-        <v>1279.2</v>
+        <v>1279.22</v>
       </c>
       <c r="T31" s="17" t="n">
         <v>141.92</v>
@@ -18374,7 +18374,7 @@
         <v/>
       </c>
       <c r="AB31" s="19">
-        <f>IF($A31="","",ROUND(N31*Parametri!$C$6,2))</f>
+        <f>IF($A31="","",ROUND(ROUND(N31,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC31" s="19">
@@ -18543,7 +18543,7 @@
         <v/>
       </c>
       <c r="AB32" s="19">
-        <f>IF($A32="","",ROUND(N32*Parametri!$C$6,2))</f>
+        <f>IF($A32="","",ROUND(ROUND(N32,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC32" s="19">
@@ -18669,19 +18669,19 @@
         <v>869.61</v>
       </c>
       <c r="O33" s="17" t="n">
-        <v>79.92</v>
+        <v>79.95</v>
       </c>
       <c r="P33" s="17" t="n">
-        <v>789.6900000000001</v>
+        <v>789.66</v>
       </c>
       <c r="Q33" s="17" t="n">
         <v>18.71</v>
       </c>
       <c r="R33" s="17" t="n">
-        <v>11.85</v>
+        <v>11.84</v>
       </c>
       <c r="S33" s="17" t="n">
-        <v>759.13</v>
+        <v>759.11</v>
       </c>
       <c r="T33" s="17" t="n">
         <v>75.15000000000001</v>
@@ -18712,7 +18712,7 @@
         <v/>
       </c>
       <c r="AB33" s="19">
-        <f>IF($A33="","",ROUND(N33*Parametri!$C$6,2))</f>
+        <f>IF($A33="","",ROUND(ROUND(N33,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC33" s="19">
@@ -18838,10 +18838,10 @@
         <v>1395.89</v>
       </c>
       <c r="O34" s="17" t="n">
-        <v>128.28</v>
+        <v>128.29</v>
       </c>
       <c r="P34" s="17" t="n">
-        <v>1267.61</v>
+        <v>1267.6</v>
       </c>
       <c r="Q34" s="17" t="n">
         <v>129.34</v>
@@ -18850,7 +18850,7 @@
         <v>19.01</v>
       </c>
       <c r="S34" s="17" t="n">
-        <v>1119.26</v>
+        <v>1119.25</v>
       </c>
       <c r="T34" s="17" t="n">
         <v>120.63</v>
@@ -18881,7 +18881,7 @@
         <v/>
       </c>
       <c r="AB34" s="19">
-        <f>IF($A34="","",ROUND(N34*Parametri!$C$6,2))</f>
+        <f>IF($A34="","",ROUND(ROUND(N34,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC34" s="19">
@@ -19007,10 +19007,10 @@
         <v>939.66</v>
       </c>
       <c r="O35" s="17" t="n">
-        <v>86.34999999999999</v>
+        <v>86.39</v>
       </c>
       <c r="P35" s="17" t="n">
-        <v>853.3099999999999</v>
+        <v>853.27</v>
       </c>
       <c r="Q35" s="17" t="n">
         <v>33.34</v>
@@ -19019,7 +19019,7 @@
         <v>12.8</v>
       </c>
       <c r="S35" s="17" t="n">
-        <v>807.17</v>
+        <v>807.13</v>
       </c>
       <c r="T35" s="17" t="n">
         <v>81.20999999999999</v>
@@ -19050,7 +19050,7 @@
         <v/>
       </c>
       <c r="AB35" s="19">
-        <f>IF($A35="","",ROUND(N35*Parametri!$C$6,2))</f>
+        <f>IF($A35="","",ROUND(ROUND(N35,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC35" s="19">
@@ -19176,19 +19176,19 @@
         <v>1802.34</v>
       </c>
       <c r="O36" s="17" t="n">
-        <v>165.64</v>
+        <v>165.6</v>
       </c>
       <c r="P36" s="17" t="n">
-        <v>1636.7</v>
+        <v>1636.74</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>228.99</v>
+        <v>229</v>
       </c>
       <c r="R36" s="17" t="n">
         <v>24.55</v>
       </c>
       <c r="S36" s="17" t="n">
-        <v>1383.16</v>
+        <v>1383.19</v>
       </c>
       <c r="T36" s="17" t="n">
         <v>155.76</v>
@@ -19219,7 +19219,7 @@
         <v/>
       </c>
       <c r="AB36" s="19">
-        <f>IF($A36="","",ROUND(N36*Parametri!$C$6,2))</f>
+        <f>IF($A36="","",ROUND(ROUND(N36,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC36" s="19">
@@ -19345,19 +19345,19 @@
         <v>2255.49</v>
       </c>
       <c r="O37" s="17" t="n">
-        <v>207.28</v>
+        <v>207.23</v>
       </c>
       <c r="P37" s="17" t="n">
-        <v>2048.21</v>
+        <v>2048.26</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>340.1</v>
+        <v>340.11</v>
       </c>
       <c r="R37" s="17" t="n">
         <v>30.72</v>
       </c>
       <c r="S37" s="17" t="n">
-        <v>1677.39</v>
+        <v>1677.43</v>
       </c>
       <c r="T37" s="17" t="n">
         <v>171.27</v>
@@ -19388,7 +19388,7 @@
         <v/>
       </c>
       <c r="AB37" s="19">
-        <f>IF($A37="","",ROUND(N37*Parametri!$C$6,2))</f>
+        <f>IF($A37="","",ROUND(ROUND(N37,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC37" s="19">
@@ -19514,19 +19514,19 @@
         <v>1486.26</v>
       </c>
       <c r="O38" s="17" t="n">
-        <v>136.59</v>
+        <v>136.56</v>
       </c>
       <c r="P38" s="17" t="n">
-        <v>1349.67</v>
+        <v>1349.7</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>151.49</v>
+        <v>151.5</v>
       </c>
       <c r="R38" s="17" t="n">
         <v>20.25</v>
       </c>
       <c r="S38" s="17" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="T38" s="17" t="n">
         <v>128.44</v>
@@ -19557,7 +19557,7 @@
         <v/>
       </c>
       <c r="AB38" s="19">
-        <f>IF($A38="","",ROUND(N38*Parametri!$C$6,2))</f>
+        <f>IF($A38="","",ROUND(ROUND(N38,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC38" s="19">
@@ -19683,10 +19683,10 @@
         <v>1001.17</v>
       </c>
       <c r="O39" s="17" t="n">
-        <v>92.01000000000001</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="P39" s="17" t="n">
-        <v>909.16</v>
+        <v>909.1799999999999</v>
       </c>
       <c r="Q39" s="17" t="n">
         <v>46.19</v>
@@ -19695,7 +19695,7 @@
         <v>13.64</v>
       </c>
       <c r="S39" s="17" t="n">
-        <v>849.33</v>
+        <v>849.35</v>
       </c>
       <c r="T39" s="17" t="n">
         <v>86.52</v>
@@ -19726,7 +19726,7 @@
         <v/>
       </c>
       <c r="AB39" s="19">
-        <f>IF($A39="","",ROUND(N39*Parametri!$C$6,2))</f>
+        <f>IF($A39="","",ROUND(ROUND(N39,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC39" s="19">
@@ -19852,19 +19852,19 @@
         <v>1472.49</v>
       </c>
       <c r="O40" s="17" t="n">
-        <v>135.32</v>
+        <v>135.28</v>
       </c>
       <c r="P40" s="17" t="n">
-        <v>1337.17</v>
+        <v>1337.21</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>148.12</v>
+        <v>148.13</v>
       </c>
       <c r="R40" s="17" t="n">
         <v>20.06</v>
       </c>
       <c r="S40" s="17" t="n">
-        <v>1168.99</v>
+        <v>1169.02</v>
       </c>
       <c r="T40" s="17" t="n">
         <v>127.25</v>
@@ -19895,7 +19895,7 @@
         <v/>
       </c>
       <c r="AB40" s="19">
-        <f>IF($A40="","",ROUND(N40*Parametri!$C$6,2))</f>
+        <f>IF($A40="","",ROUND(ROUND(N40,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC40" s="19">
@@ -20021,10 +20021,10 @@
         <v>1473.77</v>
       </c>
       <c r="O41" s="17" t="n">
-        <v>135.44</v>
+        <v>135.46</v>
       </c>
       <c r="P41" s="17" t="n">
-        <v>1338.33</v>
+        <v>1338.31</v>
       </c>
       <c r="Q41" s="17" t="n">
         <v>148.43</v>
@@ -20033,7 +20033,7 @@
         <v>20.07</v>
       </c>
       <c r="S41" s="17" t="n">
-        <v>1169.83</v>
+        <v>1169.81</v>
       </c>
       <c r="T41" s="17" t="n">
         <v>127.36</v>
@@ -20064,7 +20064,7 @@
         <v/>
       </c>
       <c r="AB41" s="19">
-        <f>IF($A41="","",ROUND(N41*Parametri!$C$6,2))</f>
+        <f>IF($A41="","",ROUND(ROUND(N41,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC41" s="19">
@@ -20190,19 +20190,19 @@
         <v>1576.76</v>
       </c>
       <c r="O42" s="17" t="n">
-        <v>144.9</v>
+        <v>144.93</v>
       </c>
       <c r="P42" s="17" t="n">
-        <v>1431.86</v>
+        <v>1431.83</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>173.69</v>
+        <v>173.68</v>
       </c>
       <c r="R42" s="17" t="n">
         <v>21.48</v>
       </c>
       <c r="S42" s="17" t="n">
-        <v>1236.69</v>
+        <v>1236.67</v>
       </c>
       <c r="T42" s="17" t="n">
         <v>136.26</v>
@@ -20233,7 +20233,7 @@
         <v/>
       </c>
       <c r="AB42" s="19">
-        <f>IF($A42="","",ROUND(N42*Parametri!$C$6,2))</f>
+        <f>IF($A42="","",ROUND(ROUND(N42,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC42" s="19">
@@ -20402,7 +20402,7 @@
         <v/>
       </c>
       <c r="AB43" s="19">
-        <f>IF($A43="","",ROUND(N43*Parametri!$C$6,2))</f>
+        <f>IF($A43="","",ROUND(ROUND(N43,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC43" s="19">
@@ -20528,19 +20528,19 @@
         <v>1922.34</v>
       </c>
       <c r="O44" s="17" t="n">
-        <v>176.66</v>
+        <v>176.63</v>
       </c>
       <c r="P44" s="17" t="n">
-        <v>1745.68</v>
+        <v>1745.71</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>258.42</v>
+        <v>258.43</v>
       </c>
       <c r="R44" s="17" t="n">
         <v>26.19</v>
       </c>
       <c r="S44" s="17" t="n">
-        <v>1461.07</v>
+        <v>1461.09</v>
       </c>
       <c r="T44" s="17" t="n">
         <v>166.13</v>
@@ -20571,7 +20571,7 @@
         <v/>
       </c>
       <c r="AB44" s="19">
-        <f>IF($A44="","",ROUND(N44*Parametri!$C$6,2))</f>
+        <f>IF($A44="","",ROUND(ROUND(N44,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC44" s="19">
@@ -20697,19 +20697,19 @@
         <v>2670.58</v>
       </c>
       <c r="O45" s="17" t="n">
-        <v>245.43</v>
+        <v>245.46</v>
       </c>
       <c r="P45" s="17" t="n">
-        <v>2425.15</v>
+        <v>2425.12</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>451.06</v>
+        <v>451.04</v>
       </c>
       <c r="R45" s="17" t="n">
         <v>36.38</v>
       </c>
       <c r="S45" s="17" t="n">
-        <v>1937.71</v>
+        <v>1937.7</v>
       </c>
       <c r="T45" s="17" t="n">
         <v>230.79</v>
@@ -20740,7 +20740,7 @@
         <v/>
       </c>
       <c r="AB45" s="19">
-        <f>IF($A45="","",ROUND(N45*Parametri!$C$6,2))</f>
+        <f>IF($A45="","",ROUND(ROUND(N45,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC45" s="19">
@@ -20866,19 +20866,19 @@
         <v>1818.61</v>
       </c>
       <c r="O46" s="17" t="n">
-        <v>167.13</v>
+        <v>167.17</v>
       </c>
       <c r="P46" s="17" t="n">
-        <v>1651.48</v>
+        <v>1651.44</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>232.98</v>
+        <v>232.97</v>
       </c>
       <c r="R46" s="17" t="n">
         <v>24.77</v>
       </c>
       <c r="S46" s="17" t="n">
-        <v>1393.73</v>
+        <v>1393.7</v>
       </c>
       <c r="T46" s="17" t="n">
         <v>157.16</v>
@@ -20909,7 +20909,7 @@
         <v/>
       </c>
       <c r="AB46" s="19">
-        <f>IF($A46="","",ROUND(N46*Parametri!$C$6,2))</f>
+        <f>IF($A46="","",ROUND(ROUND(N46,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC46" s="19">
@@ -21035,19 +21035,19 @@
         <v>1778.61</v>
       </c>
       <c r="O47" s="17" t="n">
-        <v>163.45</v>
+        <v>163.49</v>
       </c>
       <c r="P47" s="17" t="n">
-        <v>1615.16</v>
+        <v>1615.12</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>223.18</v>
+        <v>223.17</v>
       </c>
       <c r="R47" s="17" t="n">
         <v>24.23</v>
       </c>
       <c r="S47" s="17" t="n">
-        <v>1367.75</v>
+        <v>1367.72</v>
       </c>
       <c r="T47" s="17" t="n">
         <v>153.71</v>
@@ -21078,7 +21078,7 @@
         <v/>
       </c>
       <c r="AB47" s="19">
-        <f>IF($A47="","",ROUND(N47*Parametri!$C$6,2))</f>
+        <f>IF($A47="","",ROUND(ROUND(N47,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC47" s="19">
@@ -21204,19 +21204,19 @@
         <v>2577.57</v>
       </c>
       <c r="O48" s="17" t="n">
-        <v>236.88</v>
+        <v>236.92</v>
       </c>
       <c r="P48" s="17" t="n">
-        <v>2340.69</v>
+        <v>2340.65</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>419.81</v>
+        <v>419.79</v>
       </c>
       <c r="R48" s="17" t="n">
         <v>35.11</v>
       </c>
       <c r="S48" s="17" t="n">
-        <v>1885.77</v>
+        <v>1885.75</v>
       </c>
       <c r="T48" s="17" t="n">
         <v>222.75</v>
@@ -21247,7 +21247,7 @@
         <v/>
       </c>
       <c r="AB48" s="19">
-        <f>IF($A48="","",ROUND(N48*Parametri!$C$6,2))</f>
+        <f>IF($A48="","",ROUND(ROUND(N48,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC48" s="19">
@@ -21373,19 +21373,19 @@
         <v>789.58</v>
       </c>
       <c r="O49" s="17" t="n">
-        <v>72.56</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="P49" s="17" t="n">
-        <v>717.02</v>
+        <v>716.98</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R49" s="17" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="S49" s="17" t="n">
-        <v>704.26</v>
+        <v>704.24</v>
       </c>
       <c r="T49" s="17" t="n">
         <v>68.23999999999999</v>
@@ -21416,7 +21416,7 @@
         <v/>
       </c>
       <c r="AB49" s="19">
-        <f>IF($A49="","",ROUND(N49*Parametri!$C$6,2))</f>
+        <f>IF($A49="","",ROUND(ROUND(N49,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC49" s="19">
@@ -21542,13 +21542,13 @@
         <v>1827.81</v>
       </c>
       <c r="O50" s="17" t="n">
-        <v>167.98</v>
+        <v>167.99</v>
       </c>
       <c r="P50" s="17" t="n">
-        <v>1659.83</v>
+        <v>1659.82</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>235.24</v>
+        <v>235.23</v>
       </c>
       <c r="R50" s="17" t="n">
         <v>24.9</v>
@@ -21585,7 +21585,7 @@
         <v/>
       </c>
       <c r="AB50" s="19">
-        <f>IF($A50="","",ROUND(N50*Parametri!$C$6,2))</f>
+        <f>IF($A50="","",ROUND(ROUND(N50,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC50" s="19">
@@ -21711,10 +21711,10 @@
         <v>2584.07</v>
       </c>
       <c r="O51" s="17" t="n">
-        <v>237.48</v>
+        <v>237.47</v>
       </c>
       <c r="P51" s="17" t="n">
-        <v>2346.59</v>
+        <v>2346.6</v>
       </c>
       <c r="Q51" s="17" t="n">
         <v>421.99</v>
@@ -21723,7 +21723,7 @@
         <v>35.2</v>
       </c>
       <c r="S51" s="17" t="n">
-        <v>1889.4</v>
+        <v>1889.41</v>
       </c>
       <c r="T51" s="17" t="n">
         <v>223.31</v>
@@ -21754,7 +21754,7 @@
         <v/>
       </c>
       <c r="AB51" s="19">
-        <f>IF($A51="","",ROUND(N51*Parametri!$C$6,2))</f>
+        <f>IF($A51="","",ROUND(ROUND(N51,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC51" s="19">
@@ -21880,10 +21880,10 @@
         <v>963.15</v>
       </c>
       <c r="O52" s="17" t="n">
-        <v>88.51000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="P52" s="17" t="n">
-        <v>874.64</v>
+        <v>874.65</v>
       </c>
       <c r="Q52" s="17" t="n">
         <v>38.25</v>
@@ -21892,7 +21892,7 @@
         <v>13.12</v>
       </c>
       <c r="S52" s="17" t="n">
-        <v>823.27</v>
+        <v>823.28</v>
       </c>
       <c r="T52" s="17" t="n">
         <v>83.23999999999999</v>
@@ -21923,7 +21923,7 @@
         <v/>
       </c>
       <c r="AB52" s="19">
-        <f>IF($A52="","",ROUND(N52*Parametri!$C$6,2))</f>
+        <f>IF($A52="","",ROUND(ROUND(N52,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC52" s="19">
@@ -22049,19 +22049,19 @@
         <v>2799.83</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>257.3</v>
+        <v>257.32</v>
       </c>
       <c r="P53" s="17" t="n">
-        <v>2542.53</v>
+        <v>2542.51</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>494.49</v>
+        <v>494.48</v>
       </c>
       <c r="R53" s="17" t="n">
         <v>38.14</v>
       </c>
       <c r="S53" s="17" t="n">
-        <v>2009.9</v>
+        <v>2009.89</v>
       </c>
       <c r="T53" s="17" t="n">
         <v>241.96</v>
@@ -22092,7 +22092,7 @@
         <v/>
       </c>
       <c r="AB53" s="19">
-        <f>IF($A53="","",ROUND(N53*Parametri!$C$6,2))</f>
+        <f>IF($A53="","",ROUND(ROUND(N53,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC53" s="19">
@@ -22222,19 +22222,19 @@
         <v>2171.86</v>
       </c>
       <c r="O54" s="17" t="n">
-        <v>199.59</v>
+        <v>199.61</v>
       </c>
       <c r="P54" s="17" t="n">
-        <v>1972.27</v>
+        <v>1972.25</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>319.6</v>
+        <v>319.59</v>
       </c>
       <c r="R54" s="17" t="n">
         <v>29.58</v>
       </c>
       <c r="S54" s="17" t="n">
-        <v>1623.09</v>
+        <v>1623.08</v>
       </c>
       <c r="T54" s="17" t="n">
         <v>143.28</v>
@@ -22265,7 +22265,7 @@
         <v/>
       </c>
       <c r="AB54" s="19">
-        <f>IF($A54="","",ROUND(N54*Parametri!$C$6,2))</f>
+        <f>IF($A54="","",ROUND(ROUND(N54,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC54" s="19">
@@ -22391,10 +22391,10 @@
         <v>1634.83</v>
       </c>
       <c r="O55" s="17" t="n">
-        <v>150.24</v>
+        <v>150.26</v>
       </c>
       <c r="P55" s="17" t="n">
-        <v>1484.59</v>
+        <v>1484.57</v>
       </c>
       <c r="Q55" s="17" t="n">
         <v>187.92</v>
@@ -22403,7 +22403,7 @@
         <v>22.27</v>
       </c>
       <c r="S55" s="17" t="n">
-        <v>1274.4</v>
+        <v>1274.38</v>
       </c>
       <c r="T55" s="17" t="n">
         <v>141.28</v>
@@ -22434,7 +22434,7 @@
         <v/>
       </c>
       <c r="AB55" s="19">
-        <f>IF($A55="","",ROUND(N55*Parametri!$C$6,2))</f>
+        <f>IF($A55="","",ROUND(ROUND(N55,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC55" s="19">
@@ -22603,7 +22603,7 @@
         <v/>
       </c>
       <c r="AB56" s="19">
-        <f>IF($A56="","",ROUND(N56*Parametri!$C$6,2))</f>
+        <f>IF($A56="","",ROUND(ROUND(N56,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC56" s="19">
@@ -22729,13 +22729,13 @@
         <v>890.84</v>
       </c>
       <c r="O57" s="17" t="n">
-        <v>81.87</v>
+        <v>81.88</v>
       </c>
       <c r="P57" s="17" t="n">
-        <v>808.97</v>
+        <v>808.96</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>23.15</v>
+        <v>23.14</v>
       </c>
       <c r="R57" s="17" t="n">
         <v>12.13</v>
@@ -22772,7 +22772,7 @@
         <v/>
       </c>
       <c r="AB57" s="19">
-        <f>IF($A57="","",ROUND(N57*Parametri!$C$6,2))</f>
+        <f>IF($A57="","",ROUND(ROUND(N57,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC57" s="19">
@@ -22898,19 +22898,19 @@
         <v>2102.34</v>
       </c>
       <c r="O58" s="17" t="n">
-        <v>193.21</v>
+        <v>193.17</v>
       </c>
       <c r="P58" s="17" t="n">
-        <v>1909.13</v>
+        <v>1909.17</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>302.55</v>
+        <v>302.56</v>
       </c>
       <c r="R58" s="17" t="n">
         <v>28.64</v>
       </c>
       <c r="S58" s="17" t="n">
-        <v>1577.94</v>
+        <v>1577.97</v>
       </c>
       <c r="T58" s="17" t="n">
         <v>181.68</v>
@@ -22941,7 +22941,7 @@
         <v/>
       </c>
       <c r="AB58" s="19">
-        <f>IF($A58="","",ROUND(N58*Parametri!$C$6,2))</f>
+        <f>IF($A58="","",ROUND(ROUND(N58,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC58" s="19">
@@ -23067,10 +23067,10 @@
         <v>1918.91</v>
       </c>
       <c r="O59" s="17" t="n">
-        <v>176.35</v>
+        <v>176.36</v>
       </c>
       <c r="P59" s="17" t="n">
-        <v>1742.56</v>
+        <v>1742.55</v>
       </c>
       <c r="Q59" s="17" t="n">
         <v>257.57</v>
@@ -23079,7 +23079,7 @@
         <v>26.14</v>
       </c>
       <c r="S59" s="17" t="n">
-        <v>1458.85</v>
+        <v>1458.84</v>
       </c>
       <c r="T59" s="17" t="n">
         <v>165.83</v>
@@ -23110,7 +23110,7 @@
         <v/>
       </c>
       <c r="AB59" s="19">
-        <f>IF($A59="","",ROUND(N59*Parametri!$C$6,2))</f>
+        <f>IF($A59="","",ROUND(ROUND(N59,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC59" s="19">
@@ -23236,19 +23236,19 @@
         <v>1978.31</v>
       </c>
       <c r="O60" s="17" t="n">
-        <v>181.81</v>
+        <v>181.78</v>
       </c>
       <c r="P60" s="17" t="n">
-        <v>1796.5</v>
+        <v>1796.53</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>272.14</v>
+        <v>272.15</v>
       </c>
       <c r="R60" s="17" t="n">
         <v>26.95</v>
       </c>
       <c r="S60" s="17" t="n">
-        <v>1497.41</v>
+        <v>1497.43</v>
       </c>
       <c r="T60" s="17" t="n">
         <v>170.97</v>
@@ -23279,7 +23279,7 @@
         <v/>
       </c>
       <c r="AB60" s="19">
-        <f>IF($A60="","",ROUND(N60*Parametri!$C$6,2))</f>
+        <f>IF($A60="","",ROUND(ROUND(N60,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC60" s="19">
@@ -23405,19 +23405,19 @@
         <v>1559.43</v>
       </c>
       <c r="O61" s="17" t="n">
-        <v>143.31</v>
+        <v>143.27</v>
       </c>
       <c r="P61" s="17" t="n">
-        <v>1416.12</v>
+        <v>1416.16</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>169.44</v>
+        <v>169.45</v>
       </c>
       <c r="R61" s="17" t="n">
         <v>21.24</v>
       </c>
       <c r="S61" s="17" t="n">
-        <v>1225.44</v>
+        <v>1225.47</v>
       </c>
       <c r="T61" s="17" t="n">
         <v>134.77</v>
@@ -23448,7 +23448,7 @@
         <v/>
       </c>
       <c r="AB61" s="19">
-        <f>IF($A61="","",ROUND(N61*Parametri!$C$6,2))</f>
+        <f>IF($A61="","",ROUND(ROUND(N61,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC61" s="19">
@@ -23617,7 +23617,7 @@
         <v/>
       </c>
       <c r="AB62" s="19">
-        <f>IF($A62="","",ROUND(N62*Parametri!$C$6,2))</f>
+        <f>IF($A62="","",ROUND(ROUND(N62,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC62" s="19">
@@ -23743,19 +23743,19 @@
         <v>2075.74</v>
       </c>
       <c r="O63" s="17" t="n">
-        <v>190.76</v>
+        <v>190.78</v>
       </c>
       <c r="P63" s="17" t="n">
-        <v>1884.98</v>
+        <v>1884.96</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>296.03</v>
+        <v>296.02</v>
       </c>
       <c r="R63" s="17" t="n">
         <v>28.27</v>
       </c>
       <c r="S63" s="17" t="n">
-        <v>1560.68</v>
+        <v>1560.67</v>
       </c>
       <c r="T63" s="17" t="n">
         <v>171.27</v>
@@ -23786,7 +23786,7 @@
         <v/>
       </c>
       <c r="AB63" s="19">
-        <f>IF($A63="","",ROUND(N63*Parametri!$C$6,2))</f>
+        <f>IF($A63="","",ROUND(ROUND(N63,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC63" s="19">
@@ -23912,10 +23912,10 @@
         <v>1777.23</v>
       </c>
       <c r="O64" s="17" t="n">
-        <v>163.33</v>
+        <v>163.31</v>
       </c>
       <c r="P64" s="17" t="n">
-        <v>1613.9</v>
+        <v>1613.92</v>
       </c>
       <c r="Q64" s="17" t="n">
         <v>222.84</v>
@@ -23924,7 +23924,7 @@
         <v>24.21</v>
       </c>
       <c r="S64" s="17" t="n">
-        <v>1366.85</v>
+        <v>1366.87</v>
       </c>
       <c r="T64" s="17" t="n">
         <v>153.59</v>
@@ -23955,7 +23955,7 @@
         <v/>
       </c>
       <c r="AB64" s="19">
-        <f>IF($A64="","",ROUND(N64*Parametri!$C$6,2))</f>
+        <f>IF($A64="","",ROUND(ROUND(N64,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC64" s="19">
@@ -24081,19 +24081,19 @@
         <v>1486.26</v>
       </c>
       <c r="O65" s="17" t="n">
-        <v>136.59</v>
+        <v>136.56</v>
       </c>
       <c r="P65" s="17" t="n">
-        <v>1349.67</v>
+        <v>1349.7</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>151.49</v>
+        <v>151.5</v>
       </c>
       <c r="R65" s="17" t="n">
         <v>20.25</v>
       </c>
       <c r="S65" s="17" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="T65" s="17" t="n">
         <v>128.44</v>
@@ -24124,7 +24124,7 @@
         <v/>
       </c>
       <c r="AB65" s="19">
-        <f>IF($A65="","",ROUND(N65*Parametri!$C$6,2))</f>
+        <f>IF($A65="","",ROUND(ROUND(N65,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC65" s="19">
@@ -24250,19 +24250,19 @@
         <v>1882.34</v>
       </c>
       <c r="O66" s="17" t="n">
-        <v>172.99</v>
+        <v>172.96</v>
       </c>
       <c r="P66" s="17" t="n">
-        <v>1709.35</v>
+        <v>1709.38</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>248.61</v>
+        <v>248.62</v>
       </c>
       <c r="R66" s="17" t="n">
         <v>25.64</v>
       </c>
       <c r="S66" s="17" t="n">
-        <v>1435.1</v>
+        <v>1435.12</v>
       </c>
       <c r="T66" s="17" t="n">
         <v>162.67</v>
@@ -24293,7 +24293,7 @@
         <v/>
       </c>
       <c r="AB66" s="19">
-        <f>IF($A66="","",ROUND(N66*Parametri!$C$6,2))</f>
+        <f>IF($A66="","",ROUND(ROUND(N66,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC66" s="19">
@@ -24462,7 +24462,7 @@
         <v/>
       </c>
       <c r="AB67" s="19">
-        <f>IF($A67="","",ROUND(N67*Parametri!$C$6,2))</f>
+        <f>IF($A67="","",ROUND(ROUND(N67,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC67" s="19">
@@ -24631,7 +24631,7 @@
         <v/>
       </c>
       <c r="AB68" s="19">
-        <f>IF($A68="","",ROUND(N68*Parametri!$C$6,2))</f>
+        <f>IF($A68="","",ROUND(ROUND(N68,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC68" s="19">
@@ -24757,19 +24757,19 @@
         <v>1878.31</v>
       </c>
       <c r="O69" s="17" t="n">
-        <v>172.62</v>
+        <v>172.59</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>1705.69</v>
+        <v>1705.72</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>247.62</v>
+        <v>247.63</v>
       </c>
       <c r="R69" s="17" t="n">
         <v>25.59</v>
       </c>
       <c r="S69" s="17" t="n">
-        <v>1432.48</v>
+        <v>1432.5</v>
       </c>
       <c r="T69" s="17" t="n">
         <v>162.32</v>
@@ -24800,7 +24800,7 @@
         <v/>
       </c>
       <c r="AB69" s="19">
-        <f>IF($A69="","",ROUND(N69*Parametri!$C$6,2))</f>
+        <f>IF($A69="","",ROUND(ROUND(N69,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC69" s="19">
@@ -24926,10 +24926,10 @@
         <v>2279.26</v>
       </c>
       <c r="O70" s="17" t="n">
-        <v>209.46</v>
+        <v>209.44</v>
       </c>
       <c r="P70" s="17" t="n">
-        <v>2069.8</v>
+        <v>2069.82</v>
       </c>
       <c r="Q70" s="17" t="n">
         <v>345.93</v>
@@ -24938,7 +24938,7 @@
         <v>31.05</v>
       </c>
       <c r="S70" s="17" t="n">
-        <v>1692.82</v>
+        <v>1692.84</v>
       </c>
       <c r="T70" s="17" t="n">
         <v>196.97</v>
@@ -24969,7 +24969,7 @@
         <v/>
       </c>
       <c r="AB70" s="19">
-        <f>IF($A70="","",ROUND(N70*Parametri!$C$6,2))</f>
+        <f>IF($A70="","",ROUND(ROUND(N70,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC70" s="19">
@@ -25095,19 +25095,19 @@
         <v>1486.26</v>
       </c>
       <c r="O71" s="17" t="n">
-        <v>136.59</v>
+        <v>136.56</v>
       </c>
       <c r="P71" s="17" t="n">
-        <v>1349.67</v>
+        <v>1349.7</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>151.49</v>
+        <v>151.5</v>
       </c>
       <c r="R71" s="17" t="n">
         <v>20.25</v>
       </c>
       <c r="S71" s="17" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="T71" s="17" t="n">
         <v>128.44</v>
@@ -25138,7 +25138,7 @@
         <v/>
       </c>
       <c r="AB71" s="19">
-        <f>IF($A71="","",ROUND(N71*Parametri!$C$6,2))</f>
+        <f>IF($A71="","",ROUND(ROUND(N71,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC71" s="19">
@@ -25264,19 +25264,19 @@
         <v>1923.66</v>
       </c>
       <c r="O72" s="17" t="n">
-        <v>176.78</v>
+        <v>176.82</v>
       </c>
       <c r="P72" s="17" t="n">
-        <v>1746.88</v>
+        <v>1746.84</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>258.74</v>
+        <v>258.73</v>
       </c>
       <c r="R72" s="17" t="n">
         <v>26.2</v>
       </c>
       <c r="S72" s="17" t="n">
-        <v>1461.94</v>
+        <v>1461.91</v>
       </c>
       <c r="T72" s="17" t="n">
         <v>166.24</v>
@@ -25307,7 +25307,7 @@
         <v/>
       </c>
       <c r="AB72" s="19">
-        <f>IF($A72="","",ROUND(N72*Parametri!$C$6,2))</f>
+        <f>IF($A72="","",ROUND(ROUND(N72,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC72" s="19">
@@ -25433,19 +25433,19 @@
         <v>2047.62</v>
       </c>
       <c r="O73" s="17" t="n">
-        <v>188.18</v>
+        <v>188.21</v>
       </c>
       <c r="P73" s="17" t="n">
-        <v>1859.44</v>
+        <v>1859.41</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>289.13</v>
+        <v>289.12</v>
       </c>
       <c r="R73" s="17" t="n">
         <v>27.89</v>
       </c>
       <c r="S73" s="17" t="n">
-        <v>1542.42</v>
+        <v>1542.4</v>
       </c>
       <c r="T73" s="17" t="n">
         <v>176.95</v>
@@ -25476,7 +25476,7 @@
         <v/>
       </c>
       <c r="AB73" s="19">
-        <f>IF($A73="","",ROUND(N73*Parametri!$C$6,2))</f>
+        <f>IF($A73="","",ROUND(ROUND(N73,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC73" s="19">
@@ -25602,10 +25602,10 @@
         <v>1590.59</v>
       </c>
       <c r="O74" s="17" t="n">
-        <v>146.18</v>
+        <v>146.21</v>
       </c>
       <c r="P74" s="17" t="n">
-        <v>1444.41</v>
+        <v>1444.38</v>
       </c>
       <c r="Q74" s="17" t="n">
         <v>177.07</v>
@@ -25614,7 +25614,7 @@
         <v>21.67</v>
       </c>
       <c r="S74" s="17" t="n">
-        <v>1245.67</v>
+        <v>1245.64</v>
       </c>
       <c r="T74" s="17" t="n">
         <v>137.46</v>
@@ -25645,7 +25645,7 @@
         <v/>
       </c>
       <c r="AB74" s="19">
-        <f>IF($A74="","",ROUND(N74*Parametri!$C$6,2))</f>
+        <f>IF($A74="","",ROUND(ROUND(N74,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC74" s="19">
@@ -25771,10 +25771,10 @@
         <v>1082.16</v>
       </c>
       <c r="O75" s="17" t="n">
-        <v>99.45</v>
+        <v>99.44</v>
       </c>
       <c r="P75" s="17" t="n">
-        <v>982.71</v>
+        <v>982.72</v>
       </c>
       <c r="Q75" s="17" t="n">
         <v>63.11</v>
@@ -25783,7 +25783,7 @@
         <v>14.74</v>
       </c>
       <c r="S75" s="17" t="n">
-        <v>904.86</v>
+        <v>904.87</v>
       </c>
       <c r="T75" s="17" t="n">
         <v>93.52</v>
@@ -25814,7 +25814,7 @@
         <v/>
       </c>
       <c r="AB75" s="19">
-        <f>IF($A75="","",ROUND(N75*Parametri!$C$6,2))</f>
+        <f>IF($A75="","",ROUND(ROUND(N75,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC75" s="19">
@@ -25940,19 +25940,19 @@
         <v>1952.34</v>
       </c>
       <c r="O76" s="17" t="n">
-        <v>179.42</v>
+        <v>179.39</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>1772.92</v>
+        <v>1772.95</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>265.77</v>
+        <v>265.78</v>
       </c>
       <c r="R76" s="17" t="n">
         <v>26.59</v>
       </c>
       <c r="S76" s="17" t="n">
-        <v>1480.56</v>
+        <v>1480.58</v>
       </c>
       <c r="T76" s="17" t="n">
         <v>168.72</v>
@@ -25983,7 +25983,7 @@
         <v/>
       </c>
       <c r="AB76" s="19">
-        <f>IF($A76="","",ROUND(N76*Parametri!$C$6,2))</f>
+        <f>IF($A76="","",ROUND(ROUND(N76,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC76" s="19">
@@ -26109,19 +26109,19 @@
         <v>2102.34</v>
       </c>
       <c r="O77" s="17" t="n">
-        <v>193.21</v>
+        <v>193.17</v>
       </c>
       <c r="P77" s="17" t="n">
-        <v>1909.13</v>
+        <v>1909.17</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>302.55</v>
+        <v>302.56</v>
       </c>
       <c r="R77" s="17" t="n">
         <v>28.64</v>
       </c>
       <c r="S77" s="17" t="n">
-        <v>1577.94</v>
+        <v>1577.97</v>
       </c>
       <c r="T77" s="17" t="n">
         <v>181.68</v>
@@ -26152,7 +26152,7 @@
         <v/>
       </c>
       <c r="AB77" s="19">
-        <f>IF($A77="","",ROUND(N77*Parametri!$C$6,2))</f>
+        <f>IF($A77="","",ROUND(ROUND(N77,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC77" s="19">
@@ -26278,19 +26278,19 @@
         <v>2046.3</v>
       </c>
       <c r="O78" s="17" t="n">
-        <v>188.05</v>
+        <v>188.03</v>
       </c>
       <c r="P78" s="17" t="n">
-        <v>1858.25</v>
+        <v>1858.27</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>288.81</v>
+        <v>288.82</v>
       </c>
       <c r="R78" s="17" t="n">
         <v>27.87</v>
       </c>
       <c r="S78" s="17" t="n">
-        <v>1541.57</v>
+        <v>1541.58</v>
       </c>
       <c r="T78" s="17" t="n">
         <v>176.84</v>
@@ -26321,7 +26321,7 @@
         <v/>
       </c>
       <c r="AB78" s="19">
-        <f>IF($A78="","",ROUND(N78*Parametri!$C$6,2))</f>
+        <f>IF($A78="","",ROUND(ROUND(N78,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC78" s="19">
@@ -26447,19 +26447,19 @@
         <v>1905.64</v>
       </c>
       <c r="O79" s="17" t="n">
-        <v>175.13</v>
+        <v>175.16</v>
       </c>
       <c r="P79" s="17" t="n">
-        <v>1730.51</v>
+        <v>1730.48</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>254.32</v>
+        <v>254.31</v>
       </c>
       <c r="R79" s="17" t="n">
         <v>25.96</v>
       </c>
       <c r="S79" s="17" t="n">
-        <v>1450.23</v>
+        <v>1450.21</v>
       </c>
       <c r="T79" s="17" t="n">
         <v>164.68</v>
@@ -26490,7 +26490,7 @@
         <v/>
       </c>
       <c r="AB79" s="19">
-        <f>IF($A79="","",ROUND(N79*Parametri!$C$6,2))</f>
+        <f>IF($A79="","",ROUND(ROUND(N79,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC79" s="19">
@@ -26616,10 +26616,10 @@
         <v>1336.26</v>
       </c>
       <c r="O80" s="17" t="n">
-        <v>122.8</v>
+        <v>122.78</v>
       </c>
       <c r="P80" s="17" t="n">
-        <v>1213.46</v>
+        <v>1213.48</v>
       </c>
       <c r="Q80" s="17" t="n">
         <v>116.18</v>
@@ -26628,7 +26628,7 @@
         <v>18.2</v>
       </c>
       <c r="S80" s="17" t="n">
-        <v>1079.08</v>
+        <v>1079.1</v>
       </c>
       <c r="T80" s="17" t="n">
         <v>115.48</v>
@@ -26659,7 +26659,7 @@
         <v/>
       </c>
       <c r="AB80" s="19">
-        <f>IF($A80="","",ROUND(N80*Parametri!$C$6,2))</f>
+        <f>IF($A80="","",ROUND(ROUND(N80,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC80" s="19">
@@ -26789,19 +26789,19 @@
         <v>1019.61</v>
       </c>
       <c r="O81" s="17" t="n">
-        <v>93.7</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="P81" s="17" t="n">
-        <v>925.91</v>
+        <v>925.87</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>50.04</v>
+        <v>50.03</v>
       </c>
       <c r="R81" s="17" t="n">
         <v>13.89</v>
       </c>
       <c r="S81" s="17" t="n">
-        <v>861.98</v>
+        <v>861.95</v>
       </c>
       <c r="T81" s="17" t="n">
         <v>88.11</v>
@@ -26832,7 +26832,7 @@
         <v/>
       </c>
       <c r="AB81" s="19">
-        <f>IF($A81="","",ROUND(N81*Parametri!$C$6,2))</f>
+        <f>IF($A81="","",ROUND(ROUND(N81,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC81" s="19">
@@ -26958,10 +26958,10 @@
         <v>2728.91</v>
       </c>
       <c r="O82" s="17" t="n">
-        <v>250.79</v>
+        <v>250.8</v>
       </c>
       <c r="P82" s="17" t="n">
-        <v>2478.12</v>
+        <v>2478.11</v>
       </c>
       <c r="Q82" s="17" t="n">
         <v>470.65</v>
@@ -26970,7 +26970,7 @@
         <v>37.17</v>
       </c>
       <c r="S82" s="17" t="n">
-        <v>1970.3</v>
+        <v>1970.29</v>
       </c>
       <c r="T82" s="17" t="n">
         <v>235.83</v>
@@ -27001,7 +27001,7 @@
         <v/>
       </c>
       <c r="AB82" s="19">
-        <f>IF($A82="","",ROUND(N82*Parametri!$C$6,2))</f>
+        <f>IF($A82="","",ROUND(ROUND(N82,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC82" s="19">
@@ -27127,19 +27127,19 @@
         <v>2053.79</v>
       </c>
       <c r="O83" s="17" t="n">
-        <v>188.74</v>
+        <v>188.76</v>
       </c>
       <c r="P83" s="17" t="n">
-        <v>1865.05</v>
+        <v>1865.03</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>290.65</v>
+        <v>290.64</v>
       </c>
       <c r="R83" s="17" t="n">
         <v>27.98</v>
       </c>
       <c r="S83" s="17" t="n">
-        <v>1546.42</v>
+        <v>1546.41</v>
       </c>
       <c r="T83" s="17" t="n">
         <v>177.49</v>
@@ -27170,7 +27170,7 @@
         <v/>
       </c>
       <c r="AB83" s="19">
-        <f>IF($A83="","",ROUND(N83*Parametri!$C$6,2))</f>
+        <f>IF($A83="","",ROUND(ROUND(N83,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC83" s="19">
@@ -27296,10 +27296,10 @@
         <v>1572.72</v>
       </c>
       <c r="O84" s="17" t="n">
-        <v>144.53</v>
+        <v>144.56</v>
       </c>
       <c r="P84" s="17" t="n">
-        <v>1428.19</v>
+        <v>1428.16</v>
       </c>
       <c r="Q84" s="17" t="n">
         <v>172.69</v>
@@ -27308,7 +27308,7 @@
         <v>21.42</v>
       </c>
       <c r="S84" s="17" t="n">
-        <v>1234.08</v>
+        <v>1234.05</v>
       </c>
       <c r="T84" s="17" t="n">
         <v>135.91</v>
@@ -27339,7 +27339,7 @@
         <v/>
       </c>
       <c r="AB84" s="19">
-        <f>IF($A84="","",ROUND(N84*Parametri!$C$6,2))</f>
+        <f>IF($A84="","",ROUND(ROUND(N84,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC84" s="19">
@@ -27465,19 +27465,19 @@
         <v>1861.68</v>
       </c>
       <c r="O85" s="17" t="n">
-        <v>171.09</v>
+        <v>171.12</v>
       </c>
       <c r="P85" s="17" t="n">
-        <v>1690.59</v>
+        <v>1690.56</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>243.54</v>
+        <v>243.53</v>
       </c>
       <c r="R85" s="17" t="n">
         <v>25.36</v>
       </c>
       <c r="S85" s="17" t="n">
-        <v>1421.69</v>
+        <v>1421.67</v>
       </c>
       <c r="T85" s="17" t="n">
         <v>160.89</v>
@@ -27508,7 +27508,7 @@
         <v/>
       </c>
       <c r="AB85" s="19">
-        <f>IF($A85="","",ROUND(N85*Parametri!$C$6,2))</f>
+        <f>IF($A85="","",ROUND(ROUND(N85,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC85" s="19">
@@ -27634,19 +27634,19 @@
         <v>1421.58</v>
       </c>
       <c r="O86" s="17" t="n">
-        <v>130.64</v>
+        <v>130.68</v>
       </c>
       <c r="P86" s="17" t="n">
-        <v>1290.94</v>
+        <v>1290.9</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>135.64</v>
+        <v>135.63</v>
       </c>
       <c r="R86" s="17" t="n">
         <v>19.36</v>
       </c>
       <c r="S86" s="17" t="n">
-        <v>1135.94</v>
+        <v>1135.91</v>
       </c>
       <c r="T86" s="17" t="n">
         <v>122.85</v>
@@ -27677,7 +27677,7 @@
         <v/>
       </c>
       <c r="AB86" s="19">
-        <f>IF($A86="","",ROUND(N86*Parametri!$C$6,2))</f>
+        <f>IF($A86="","",ROUND(ROUND(N86,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC86" s="19">
@@ -27803,19 +27803,19 @@
         <v>1802.34</v>
       </c>
       <c r="O87" s="17" t="n">
-        <v>165.64</v>
+        <v>165.6</v>
       </c>
       <c r="P87" s="17" t="n">
-        <v>1636.7</v>
+        <v>1636.74</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>228.99</v>
+        <v>229</v>
       </c>
       <c r="R87" s="17" t="n">
         <v>24.55</v>
       </c>
       <c r="S87" s="17" t="n">
-        <v>1383.16</v>
+        <v>1383.19</v>
       </c>
       <c r="T87" s="17" t="n">
         <v>155.76</v>
@@ -27846,7 +27846,7 @@
         <v/>
       </c>
       <c r="AB87" s="19">
-        <f>IF($A87="","",ROUND(N87*Parametri!$C$6,2))</f>
+        <f>IF($A87="","",ROUND(ROUND(N87,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC87" s="19">
@@ -27972,19 +27972,19 @@
         <v>2064.32</v>
       </c>
       <c r="O88" s="17" t="n">
-        <v>189.71</v>
+        <v>189.68</v>
       </c>
       <c r="P88" s="17" t="n">
-        <v>1874.61</v>
+        <v>1874.64</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>293.23</v>
+        <v>293.24</v>
       </c>
       <c r="R88" s="17" t="n">
         <v>28.12</v>
       </c>
       <c r="S88" s="17" t="n">
-        <v>1553.26</v>
+        <v>1553.28</v>
       </c>
       <c r="T88" s="17" t="n">
         <v>178.4</v>
@@ -28015,7 +28015,7 @@
         <v/>
       </c>
       <c r="AB88" s="19">
-        <f>IF($A88="","",ROUND(N88*Parametri!$C$6,2))</f>
+        <f>IF($A88="","",ROUND(ROUND(N88,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC88" s="19">
@@ -28141,19 +28141,19 @@
         <v>951.5</v>
       </c>
       <c r="O89" s="17" t="n">
-        <v>87.44</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="P89" s="17" t="n">
-        <v>864.0599999999999</v>
+        <v>864.01</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>35.82</v>
+        <v>35.81</v>
       </c>
       <c r="R89" s="17" t="n">
         <v>12.96</v>
       </c>
       <c r="S89" s="17" t="n">
-        <v>815.28</v>
+        <v>815.24</v>
       </c>
       <c r="T89" s="17" t="n">
         <v>82.23</v>
@@ -28184,7 +28184,7 @@
         <v/>
       </c>
       <c r="AB89" s="19">
-        <f>IF($A89="","",ROUND(N89*Parametri!$C$6,2))</f>
+        <f>IF($A89="","",ROUND(ROUND(N89,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC89" s="19">
@@ -28310,19 +28310,19 @@
         <v>1802.34</v>
       </c>
       <c r="O90" s="17" t="n">
-        <v>165.64</v>
+        <v>165.6</v>
       </c>
       <c r="P90" s="17" t="n">
-        <v>1636.7</v>
+        <v>1636.74</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>228.99</v>
+        <v>229</v>
       </c>
       <c r="R90" s="17" t="n">
         <v>24.55</v>
       </c>
       <c r="S90" s="17" t="n">
-        <v>1383.16</v>
+        <v>1383.19</v>
       </c>
       <c r="T90" s="17" t="n">
         <v>155.76</v>
@@ -28353,7 +28353,7 @@
         <v/>
       </c>
       <c r="AB90" s="19">
-        <f>IF($A90="","",ROUND(N90*Parametri!$C$6,2))</f>
+        <f>IF($A90="","",ROUND(ROUND(N90,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC90" s="19">
@@ -28479,10 +28479,10 @@
         <v>1367.25</v>
       </c>
       <c r="O91" s="17" t="n">
-        <v>129.75</v>
+        <v>129.73</v>
       </c>
       <c r="P91" s="17" t="n">
-        <v>1237.5</v>
+        <v>1237.52</v>
       </c>
       <c r="Q91" s="17" t="n">
         <v>121.71</v>
@@ -28491,7 +28491,7 @@
         <v>18.56</v>
       </c>
       <c r="S91" s="17" t="n">
-        <v>1097.23</v>
+        <v>1097.25</v>
       </c>
       <c r="T91" s="17" t="n">
         <v>118.16</v>
@@ -28522,7 +28522,7 @@
         <v/>
       </c>
       <c r="AB91" s="19">
-        <f>IF($A91="","",ROUND(N91*Parametri!$C$6,2))</f>
+        <f>IF($A91="","",ROUND(ROUND(N91,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC91" s="19">
@@ -28648,10 +28648,10 @@
         <v>932.16</v>
       </c>
       <c r="O92" s="17" t="n">
-        <v>85.67</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="P92" s="17" t="n">
-        <v>846.49</v>
+        <v>846.51</v>
       </c>
       <c r="Q92" s="17" t="n">
         <v>31.78</v>
@@ -28660,7 +28660,7 @@
         <v>12.7</v>
       </c>
       <c r="S92" s="17" t="n">
-        <v>802.01</v>
+        <v>802.03</v>
       </c>
       <c r="T92" s="17" t="n">
         <v>80.56</v>
@@ -28691,7 +28691,7 @@
         <v/>
       </c>
       <c r="AB92" s="19">
-        <f>IF($A92="","",ROUND(N92*Parametri!$C$6,2))</f>
+        <f>IF($A92="","",ROUND(ROUND(N92,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC92" s="19">
@@ -28817,19 +28817,19 @@
         <v>1371.24</v>
       </c>
       <c r="O93" s="17" t="n">
-        <v>126.02</v>
+        <v>125.99</v>
       </c>
       <c r="P93" s="17" t="n">
-        <v>1245.22</v>
+        <v>1245.25</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>123.48</v>
+        <v>123.49</v>
       </c>
       <c r="R93" s="17" t="n">
         <v>18.68</v>
       </c>
       <c r="S93" s="17" t="n">
-        <v>1103.06</v>
+        <v>1103.08</v>
       </c>
       <c r="T93" s="17" t="n">
         <v>118.5</v>
@@ -28860,7 +28860,7 @@
         <v/>
       </c>
       <c r="AB93" s="19">
-        <f>IF($A93="","",ROUND(N93*Parametri!$C$6,2))</f>
+        <f>IF($A93="","",ROUND(ROUND(N93,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC93" s="19">
@@ -28986,19 +28986,19 @@
         <v>3453.24</v>
       </c>
       <c r="O94" s="17" t="n">
-        <v>317.35</v>
+        <v>317.33</v>
       </c>
       <c r="P94" s="17" t="n">
-        <v>3135.89</v>
+        <v>3135.91</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>714.03</v>
+        <v>714.04</v>
       </c>
       <c r="R94" s="17" t="n">
         <v>47.04</v>
       </c>
       <c r="S94" s="17" t="n">
-        <v>2374.82</v>
+        <v>2374.83</v>
       </c>
       <c r="T94" s="17" t="n">
         <v>206.84</v>
@@ -29029,7 +29029,7 @@
         <v/>
       </c>
       <c r="AB94" s="19">
-        <f>IF($A94="","",ROUND(N94*Parametri!$C$6,2))</f>
+        <f>IF($A94="","",ROUND(ROUND(N94,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC94" s="19">
@@ -29155,19 +29155,19 @@
         <v>1728.31</v>
       </c>
       <c r="O95" s="17" t="n">
-        <v>158.83</v>
+        <v>158.8</v>
       </c>
       <c r="P95" s="17" t="n">
-        <v>1569.48</v>
+        <v>1569.51</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>210.84</v>
+        <v>210.85</v>
       </c>
       <c r="R95" s="17" t="n">
         <v>23.54</v>
       </c>
       <c r="S95" s="17" t="n">
-        <v>1335.1</v>
+        <v>1335.12</v>
       </c>
       <c r="T95" s="17" t="n">
         <v>149.36</v>
@@ -29198,7 +29198,7 @@
         <v/>
       </c>
       <c r="AB95" s="19">
-        <f>IF($A95="","",ROUND(N95*Parametri!$C$6,2))</f>
+        <f>IF($A95="","",ROUND(ROUND(N95,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC95" s="19">
@@ -29324,19 +29324,19 @@
         <v>1809.51</v>
       </c>
       <c r="O96" s="17" t="n">
-        <v>166.29</v>
+        <v>166.34</v>
       </c>
       <c r="P96" s="17" t="n">
-        <v>1643.22</v>
+        <v>1643.17</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>230.75</v>
+        <v>230.74</v>
       </c>
       <c r="R96" s="17" t="n">
         <v>24.65</v>
       </c>
       <c r="S96" s="17" t="n">
-        <v>1387.82</v>
+        <v>1387.78</v>
       </c>
       <c r="T96" s="17" t="n">
         <v>156.38</v>
@@ -29367,7 +29367,7 @@
         <v/>
       </c>
       <c r="AB96" s="19">
-        <f>IF($A96="","",ROUND(N96*Parametri!$C$6,2))</f>
+        <f>IF($A96="","",ROUND(ROUND(N96,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC96" s="19">
@@ -29493,19 +29493,19 @@
         <v>2025.74</v>
       </c>
       <c r="O97" s="17" t="n">
-        <v>186.17</v>
+        <v>186.19</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>1839.57</v>
+        <v>1839.55</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>283.77</v>
+        <v>283.76</v>
       </c>
       <c r="R97" s="17" t="n">
         <v>27.59</v>
       </c>
       <c r="S97" s="17" t="n">
-        <v>1628.21</v>
+        <v>1628.2</v>
       </c>
       <c r="T97" s="17" t="n">
         <v>175.06</v>
@@ -29536,7 +29536,7 @@
         <v/>
       </c>
       <c r="AB97" s="19">
-        <f>IF($A97="","",ROUND(N97*Parametri!$C$6,2))</f>
+        <f>IF($A97="","",ROUND(ROUND(N97,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC97" s="19">
@@ -29662,19 +29662,19 @@
         <v>1023.85</v>
       </c>
       <c r="O98" s="17" t="n">
-        <v>94.09</v>
+        <v>94.11</v>
       </c>
       <c r="P98" s="17" t="n">
-        <v>929.76</v>
+        <v>929.74</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>50.93</v>
+        <v>50.92</v>
       </c>
       <c r="R98" s="17" t="n">
         <v>13.95</v>
       </c>
       <c r="S98" s="17" t="n">
-        <v>864.88</v>
+        <v>864.87</v>
       </c>
       <c r="T98" s="17" t="n">
         <v>88.48</v>
@@ -29705,7 +29705,7 @@
         <v/>
       </c>
       <c r="AB98" s="19">
-        <f>IF($A98="","",ROUND(N98*Parametri!$C$6,2))</f>
+        <f>IF($A98="","",ROUND(ROUND(N98,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC98" s="19">
@@ -29831,13 +29831,13 @@
         <v>1076.9</v>
       </c>
       <c r="O99" s="17" t="n">
-        <v>98.97</v>
+        <v>98.98</v>
       </c>
       <c r="P99" s="17" t="n">
-        <v>977.9299999999999</v>
+        <v>977.92</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>62.01</v>
+        <v>62</v>
       </c>
       <c r="R99" s="17" t="n">
         <v>14.67</v>
@@ -29874,7 +29874,7 @@
         <v/>
       </c>
       <c r="AB99" s="19">
-        <f>IF($A99="","",ROUND(N99*Parametri!$C$6,2))</f>
+        <f>IF($A99="","",ROUND(ROUND(N99,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC99" s="19">
@@ -30000,19 +30000,19 @@
         <v>1963.66</v>
       </c>
       <c r="O100" s="17" t="n">
-        <v>180.46</v>
+        <v>180.49</v>
       </c>
       <c r="P100" s="17" t="n">
-        <v>1783.2</v>
+        <v>1783.17</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>268.55</v>
+        <v>268.54</v>
       </c>
       <c r="R100" s="17" t="n">
         <v>26.75</v>
       </c>
       <c r="S100" s="17" t="n">
-        <v>1487.9</v>
+        <v>1487.88</v>
       </c>
       <c r="T100" s="17" t="n">
         <v>169.7</v>
@@ -30043,7 +30043,7 @@
         <v/>
       </c>
       <c r="AB100" s="19">
-        <f>IF($A100="","",ROUND(N100*Parametri!$C$6,2))</f>
+        <f>IF($A100="","",ROUND(ROUND(N100,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC100" s="19">
@@ -30212,7 +30212,7 @@
         <v/>
       </c>
       <c r="AB101" s="19">
-        <f>IF($A101="","",ROUND(N101*Parametri!$C$6,2))</f>
+        <f>IF($A101="","",ROUND(ROUND(N101,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC101" s="19">
@@ -30338,19 +30338,19 @@
         <v>2163.54</v>
       </c>
       <c r="O102" s="17" t="n">
-        <v>205.32</v>
+        <v>205.36</v>
       </c>
       <c r="P102" s="17" t="n">
-        <v>1958.22</v>
+        <v>1958.18</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>315.8</v>
+        <v>315.79</v>
       </c>
       <c r="R102" s="17" t="n">
         <v>29.37</v>
       </c>
       <c r="S102" s="17" t="n">
-        <v>1613.05</v>
+        <v>1613.02</v>
       </c>
       <c r="T102" s="17" t="n">
         <v>186.97</v>
@@ -30381,7 +30381,7 @@
         <v/>
       </c>
       <c r="AB102" s="19">
-        <f>IF($A102="","",ROUND(N102*Parametri!$C$6,2))</f>
+        <f>IF($A102="","",ROUND(ROUND(N102,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC102" s="19">
@@ -30507,16 +30507,16 @@
         <v>2862.76</v>
       </c>
       <c r="O103" s="17" t="n">
-        <v>263.09</v>
+        <v>263.11</v>
       </c>
       <c r="P103" s="17" t="n">
-        <v>2599.67</v>
+        <v>2599.65</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>515.63</v>
+        <v>515.62</v>
       </c>
       <c r="R103" s="17" t="n">
-        <v>39</v>
+        <v>38.99</v>
       </c>
       <c r="S103" s="17" t="n">
         <v>2045.04</v>
@@ -30550,7 +30550,7 @@
         <v/>
       </c>
       <c r="AB103" s="19">
-        <f>IF($A103="","",ROUND(N103*Parametri!$C$6,2))</f>
+        <f>IF($A103="","",ROUND(ROUND(N103,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC103" s="19">
@@ -30676,19 +30676,19 @@
         <v>1408.74</v>
       </c>
       <c r="O104" s="17" t="n">
-        <v>129.46</v>
+        <v>129.49</v>
       </c>
       <c r="P104" s="17" t="n">
-        <v>1279.28</v>
+        <v>1279.25</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>132.49</v>
+        <v>132.48</v>
       </c>
       <c r="R104" s="17" t="n">
         <v>19.19</v>
       </c>
       <c r="S104" s="17" t="n">
-        <v>1127.6</v>
+        <v>1127.58</v>
       </c>
       <c r="T104" s="17" t="n">
         <v>121.74</v>
@@ -30719,7 +30719,7 @@
         <v/>
       </c>
       <c r="AB104" s="19">
-        <f>IF($A104="","",ROUND(N104*Parametri!$C$6,2))</f>
+        <f>IF($A104="","",ROUND(ROUND(N104,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC104" s="19">
@@ -30845,10 +30845,10 @@
         <v>1819.21</v>
       </c>
       <c r="O105" s="17" t="n">
-        <v>167.19</v>
+        <v>167.17</v>
       </c>
       <c r="P105" s="17" t="n">
-        <v>1652.02</v>
+        <v>1652.04</v>
       </c>
       <c r="Q105" s="17" t="n">
         <v>233.13</v>
@@ -30857,7 +30857,7 @@
         <v>24.78</v>
       </c>
       <c r="S105" s="17" t="n">
-        <v>1394.11</v>
+        <v>1394.13</v>
       </c>
       <c r="T105" s="17" t="n">
         <v>143.28</v>
@@ -30888,7 +30888,7 @@
         <v/>
       </c>
       <c r="AB105" s="19">
-        <f>IF($A105="","",ROUND(N105*Parametri!$C$6,2))</f>
+        <f>IF($A105="","",ROUND(ROUND(N105,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC105" s="19">
@@ -31057,7 +31057,7 @@
         <v/>
       </c>
       <c r="AB106" s="19">
-        <f>IF($A106="","",ROUND(N106*Parametri!$C$6,2))</f>
+        <f>IF($A106="","",ROUND(ROUND(N106,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC106" s="19">
@@ -31183,10 +31183,10 @@
         <v>1746.95</v>
       </c>
       <c r="O107" s="17" t="n">
-        <v>160.54</v>
+        <v>160.55</v>
       </c>
       <c r="P107" s="17" t="n">
-        <v>1586.41</v>
+        <v>1586.4</v>
       </c>
       <c r="Q107" s="17" t="n">
         <v>215.41</v>
@@ -31195,7 +31195,7 @@
         <v>23.8</v>
       </c>
       <c r="S107" s="17" t="n">
-        <v>1347.2</v>
+        <v>1347.19</v>
       </c>
       <c r="T107" s="17" t="n">
         <v>150.97</v>
@@ -31226,7 +31226,7 @@
         <v/>
       </c>
       <c r="AB107" s="19">
-        <f>IF($A107="","",ROUND(N107*Parametri!$C$6,2))</f>
+        <f>IF($A107="","",ROUND(ROUND(N107,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC107" s="19">
@@ -31352,13 +31352,13 @@
         <v>1046.92</v>
       </c>
       <c r="O108" s="17" t="n">
-        <v>96.20999999999999</v>
+        <v>96.22</v>
       </c>
       <c r="P108" s="17" t="n">
-        <v>950.71</v>
+        <v>950.7</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>55.75</v>
+        <v>55.74</v>
       </c>
       <c r="R108" s="17" t="n">
         <v>14.26</v>
@@ -31395,7 +31395,7 @@
         <v/>
       </c>
       <c r="AB108" s="19">
-        <f>IF($A108="","",ROUND(N108*Parametri!$C$6,2))</f>
+        <f>IF($A108="","",ROUND(ROUND(N108,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC108" s="19">
@@ -31521,13 +31521,13 @@
         <v>3048.91</v>
       </c>
       <c r="O109" s="17" t="n">
-        <v>280.19</v>
+        <v>280.2</v>
       </c>
       <c r="P109" s="17" t="n">
-        <v>2768.72</v>
+        <v>2768.71</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>578.1799999999999</v>
+        <v>578.17</v>
       </c>
       <c r="R109" s="17" t="n">
         <v>41.53</v>
@@ -31564,7 +31564,7 @@
         <v/>
       </c>
       <c r="AB109" s="19">
-        <f>IF($A109="","",ROUND(N109*Parametri!$C$6,2))</f>
+        <f>IF($A109="","",ROUND(ROUND(N109,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC109" s="19">
@@ -31690,19 +31690,19 @@
         <v>1864.32</v>
       </c>
       <c r="O110" s="17" t="n">
-        <v>171.33</v>
+        <v>171.3</v>
       </c>
       <c r="P110" s="17" t="n">
-        <v>1692.99</v>
+        <v>1693.02</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>244.19</v>
+        <v>244.2</v>
       </c>
       <c r="R110" s="17" t="n">
-        <v>25.39</v>
+        <v>25.4</v>
       </c>
       <c r="S110" s="17" t="n">
-        <v>1423.41</v>
+        <v>1423.42</v>
       </c>
       <c r="T110" s="17" t="n">
         <v>161.11</v>
@@ -31733,7 +31733,7 @@
         <v/>
       </c>
       <c r="AB110" s="19">
-        <f>IF($A110="","",ROUND(N110*Parametri!$C$6,2))</f>
+        <f>IF($A110="","",ROUND(ROUND(N110,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC110" s="19">
@@ -31902,7 +31902,7 @@
         <v/>
       </c>
       <c r="AB111" s="19">
-        <f>IF($A111="","",ROUND(N111*Parametri!$C$6,2))</f>
+        <f>IF($A111="","",ROUND(ROUND(N111,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC111" s="19">
@@ -32028,19 +32028,19 @@
         <v>1688.35</v>
       </c>
       <c r="O112" s="17" t="n">
-        <v>155.16</v>
+        <v>155.13</v>
       </c>
       <c r="P112" s="17" t="n">
-        <v>1533.19</v>
+        <v>1533.22</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>201.04</v>
+        <v>201.05</v>
       </c>
       <c r="R112" s="17" t="n">
         <v>23</v>
       </c>
       <c r="S112" s="17" t="n">
-        <v>1309.15</v>
+        <v>1309.17</v>
       </c>
       <c r="T112" s="17" t="n">
         <v>145.91</v>
@@ -32071,7 +32071,7 @@
         <v/>
       </c>
       <c r="AB112" s="19">
-        <f>IF($A112="","",ROUND(N112*Parametri!$C$6,2))</f>
+        <f>IF($A112="","",ROUND(ROUND(N112,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC112" s="19">
@@ -32240,7 +32240,7 @@
         <v/>
       </c>
       <c r="AB113" s="19">
-        <f>IF($A113="","",ROUND(N113*Parametri!$C$6,2))</f>
+        <f>IF($A113="","",ROUND(ROUND(N113,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC113" s="19">
@@ -32370,10 +32370,10 @@
         <v>2192.82</v>
       </c>
       <c r="O114" s="17" t="n">
-        <v>201.52</v>
+        <v>201.54</v>
       </c>
       <c r="P114" s="17" t="n">
-        <v>1991.3</v>
+        <v>1991.28</v>
       </c>
       <c r="Q114" s="17" t="n">
         <v>324.73</v>
@@ -32382,7 +32382,7 @@
         <v>29.87</v>
       </c>
       <c r="S114" s="17" t="n">
-        <v>1636.7</v>
+        <v>1636.68</v>
       </c>
       <c r="T114" s="17" t="n">
         <v>146.79</v>
@@ -32413,7 +32413,7 @@
         <v/>
       </c>
       <c r="AB114" s="19">
-        <f>IF($A114="","",ROUND(N114*Parametri!$C$6,2))</f>
+        <f>IF($A114="","",ROUND(ROUND(N114,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC114" s="19">
@@ -32539,19 +32539,19 @@
         <v>2157.44</v>
       </c>
       <c r="O115" s="17" t="n">
-        <v>198.27</v>
+        <v>198.23</v>
       </c>
       <c r="P115" s="17" t="n">
-        <v>1959.17</v>
+        <v>1959.21</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>316.06</v>
+        <v>316.07</v>
       </c>
       <c r="R115" s="17" t="n">
         <v>29.39</v>
       </c>
       <c r="S115" s="17" t="n">
-        <v>1613.72</v>
+        <v>1613.75</v>
       </c>
       <c r="T115" s="17" t="n">
         <v>186.45</v>
@@ -32582,7 +32582,7 @@
         <v/>
       </c>
       <c r="AB115" s="19">
-        <f>IF($A115="","",ROUND(N115*Parametri!$C$6,2))</f>
+        <f>IF($A115="","",ROUND(ROUND(N115,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC115" s="19">
@@ -32751,7 +32751,7 @@
         <v/>
       </c>
       <c r="AB116" s="19">
-        <f>IF($A116="","",ROUND(N116*Parametri!$C$6,2))</f>
+        <f>IF($A116="","",ROUND(ROUND(N116,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC116" s="19">
@@ -32877,19 +32877,19 @@
         <v>2025.74</v>
       </c>
       <c r="O117" s="17" t="n">
-        <v>186.17</v>
+        <v>186.19</v>
       </c>
       <c r="P117" s="17" t="n">
-        <v>1839.57</v>
+        <v>1839.55</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>283.77</v>
+        <v>283.76</v>
       </c>
       <c r="R117" s="17" t="n">
         <v>27.59</v>
       </c>
       <c r="S117" s="17" t="n">
-        <v>1528.21</v>
+        <v>1528.2</v>
       </c>
       <c r="T117" s="17" t="n">
         <v>175.06</v>
@@ -32920,7 +32920,7 @@
         <v/>
       </c>
       <c r="AB117" s="19">
-        <f>IF($A117="","",ROUND(N117*Parametri!$C$6,2))</f>
+        <f>IF($A117="","",ROUND(ROUND(N117,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC117" s="19">
@@ -33046,19 +33046,19 @@
         <v>2069.64</v>
       </c>
       <c r="O118" s="17" t="n">
-        <v>190.2</v>
+        <v>190.23</v>
       </c>
       <c r="P118" s="17" t="n">
-        <v>1879.44</v>
+        <v>1879.41</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>294.53</v>
+        <v>294.52</v>
       </c>
       <c r="R118" s="17" t="n">
         <v>28.19</v>
       </c>
       <c r="S118" s="17" t="n">
-        <v>1556.72</v>
+        <v>1556.7</v>
       </c>
       <c r="T118" s="17" t="n">
         <v>178.86</v>
@@ -33089,7 +33089,7 @@
         <v/>
       </c>
       <c r="AB118" s="19">
-        <f>IF($A118="","",ROUND(N118*Parametri!$C$6,2))</f>
+        <f>IF($A118="","",ROUND(ROUND(N118,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC118" s="19">
@@ -33215,19 +33215,19 @@
         <v>1532.18</v>
       </c>
       <c r="O119" s="17" t="n">
-        <v>140.81</v>
+        <v>140.79</v>
       </c>
       <c r="P119" s="17" t="n">
-        <v>1391.37</v>
+        <v>1391.39</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>162.75</v>
+        <v>162.76</v>
       </c>
       <c r="R119" s="17" t="n">
         <v>20.87</v>
       </c>
       <c r="S119" s="17" t="n">
-        <v>1207.75</v>
+        <v>1207.76</v>
       </c>
       <c r="T119" s="17" t="n">
         <v>132.41</v>
@@ -33258,7 +33258,7 @@
         <v/>
       </c>
       <c r="AB119" s="19">
-        <f>IF($A119="","",ROUND(N119*Parametri!$C$6,2))</f>
+        <f>IF($A119="","",ROUND(ROUND(N119,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC119" s="19">
@@ -33384,10 +33384,10 @@
         <v>2225.74</v>
       </c>
       <c r="O120" s="17" t="n">
-        <v>204.55</v>
+        <v>204.57</v>
       </c>
       <c r="P120" s="17" t="n">
-        <v>2021.19</v>
+        <v>2021.17</v>
       </c>
       <c r="Q120" s="17" t="n">
         <v>332.8</v>
@@ -33396,7 +33396,7 @@
         <v>30.32</v>
       </c>
       <c r="S120" s="17" t="n">
-        <v>1658.07</v>
+        <v>1658.05</v>
       </c>
       <c r="T120" s="17" t="n">
         <v>192.35</v>
@@ -33427,7 +33427,7 @@
         <v/>
       </c>
       <c r="AB120" s="19">
-        <f>IF($A120="","",ROUND(N120*Parametri!$C$6,2))</f>
+        <f>IF($A120="","",ROUND(ROUND(N120,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC120" s="19">
@@ -33553,10 +33553,10 @@
         <v>1395.89</v>
       </c>
       <c r="O121" s="17" t="n">
-        <v>128.28</v>
+        <v>128.29</v>
       </c>
       <c r="P121" s="17" t="n">
-        <v>1267.61</v>
+        <v>1267.6</v>
       </c>
       <c r="Q121" s="17" t="n">
         <v>129.34</v>
@@ -33565,7 +33565,7 @@
         <v>19.01</v>
       </c>
       <c r="S121" s="17" t="n">
-        <v>1119.26</v>
+        <v>1119.25</v>
       </c>
       <c r="T121" s="17" t="n">
         <v>120.63</v>
@@ -33596,7 +33596,7 @@
         <v/>
       </c>
       <c r="AB121" s="19">
-        <f>IF($A121="","",ROUND(N121*Parametri!$C$6,2))</f>
+        <f>IF($A121="","",ROUND(ROUND(N121,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC121" s="19">
@@ -33765,7 +33765,7 @@
         <v/>
       </c>
       <c r="AB122" s="19">
-        <f>IF($A122="","",ROUND(N122*Parametri!$C$6,2))</f>
+        <f>IF($A122="","",ROUND(ROUND(N122,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC122" s="19">
@@ -33891,19 +33891,19 @@
         <v>2153.79</v>
       </c>
       <c r="O123" s="17" t="n">
-        <v>197.93</v>
+        <v>197.95</v>
       </c>
       <c r="P123" s="17" t="n">
-        <v>1955.86</v>
+        <v>1955.84</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>315.17</v>
+        <v>315.16</v>
       </c>
       <c r="R123" s="17" t="n">
         <v>29.34</v>
       </c>
       <c r="S123" s="17" t="n">
-        <v>1611.35</v>
+        <v>1611.34</v>
       </c>
       <c r="T123" s="17" t="n">
         <v>186.13</v>
@@ -33934,7 +33934,7 @@
         <v/>
       </c>
       <c r="AB123" s="19">
-        <f>IF($A123="","",ROUND(N123*Parametri!$C$6,2))</f>
+        <f>IF($A123="","",ROUND(ROUND(N123,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC123" s="19">
@@ -34107,7 +34107,7 @@
         <v/>
       </c>
       <c r="AB124" s="19">
-        <f>IF($A124="","",ROUND(N124*Parametri!$C$6,2))</f>
+        <f>IF($A124="","",ROUND(ROUND(N124,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC124" s="19">
@@ -34280,7 +34280,7 @@
         <v/>
       </c>
       <c r="AB125" s="19">
-        <f>IF($A125="","",ROUND(N125*Parametri!$C$6,2))</f>
+        <f>IF($A125="","",ROUND(ROUND(N125,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC125" s="19">
@@ -34453,7 +34453,7 @@
         <v/>
       </c>
       <c r="AB126" s="19">
-        <f>IF($A126="","",ROUND(N126*Parametri!$C$6,2))</f>
+        <f>IF($A126="","",ROUND(ROUND(N126,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC126" s="19">
@@ -34547,7 +34547,7 @@
         <v/>
       </c>
       <c r="AB127" s="19">
-        <f>IF($A127="","",ROUND(N127*Parametri!$C$6,2))</f>
+        <f>IF($A127="","",ROUND(ROUND(N127,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC127" s="19">
@@ -34641,7 +34641,7 @@
         <v/>
       </c>
       <c r="AB128" s="19">
-        <f>IF($A128="","",ROUND(N128*Parametri!$C$6,2))</f>
+        <f>IF($A128="","",ROUND(ROUND(N128,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC128" s="19">
@@ -34735,7 +34735,7 @@
         <v/>
       </c>
       <c r="AB129" s="19">
-        <f>IF($A129="","",ROUND(N129*Parametri!$C$6,2))</f>
+        <f>IF($A129="","",ROUND(ROUND(N129,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC129" s="19">
@@ -34829,7 +34829,7 @@
         <v/>
       </c>
       <c r="AB130" s="19">
-        <f>IF($A130="","",ROUND(N130*Parametri!$C$6,2))</f>
+        <f>IF($A130="","",ROUND(ROUND(N130,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC130" s="19">
@@ -34923,7 +34923,7 @@
         <v/>
       </c>
       <c r="AB131" s="19">
-        <f>IF($A131="","",ROUND(N131*Parametri!$C$6,2))</f>
+        <f>IF($A131="","",ROUND(ROUND(N131,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC131" s="19">
@@ -35017,7 +35017,7 @@
         <v/>
       </c>
       <c r="AB132" s="19">
-        <f>IF($A132="","",ROUND(N132*Parametri!$C$6,2))</f>
+        <f>IF($A132="","",ROUND(ROUND(N132,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC132" s="19">
@@ -35111,7 +35111,7 @@
         <v/>
       </c>
       <c r="AB133" s="19">
-        <f>IF($A133="","",ROUND(N133*Parametri!$C$6,2))</f>
+        <f>IF($A133="","",ROUND(ROUND(N133,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC133" s="19">
@@ -35205,7 +35205,7 @@
         <v/>
       </c>
       <c r="AB134" s="19">
-        <f>IF($A134="","",ROUND(N134*Parametri!$C$6,2))</f>
+        <f>IF($A134="","",ROUND(ROUND(N134,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC134" s="19">
@@ -35299,7 +35299,7 @@
         <v/>
       </c>
       <c r="AB135" s="19">
-        <f>IF($A135="","",ROUND(N135*Parametri!$C$6,2))</f>
+        <f>IF($A135="","",ROUND(ROUND(N135,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC135" s="19">
@@ -35393,7 +35393,7 @@
         <v/>
       </c>
       <c r="AB136" s="19">
-        <f>IF($A136="","",ROUND(N136*Parametri!$C$6,2))</f>
+        <f>IF($A136="","",ROUND(ROUND(N136,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC136" s="19">
@@ -35487,7 +35487,7 @@
         <v/>
       </c>
       <c r="AB137" s="19">
-        <f>IF($A137="","",ROUND(N137*Parametri!$C$6,2))</f>
+        <f>IF($A137="","",ROUND(ROUND(N137,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC137" s="19">
@@ -35581,7 +35581,7 @@
         <v/>
       </c>
       <c r="AB138" s="19">
-        <f>IF($A138="","",ROUND(N138*Parametri!$C$6,2))</f>
+        <f>IF($A138="","",ROUND(ROUND(N138,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC138" s="19">
@@ -35675,7 +35675,7 @@
         <v/>
       </c>
       <c r="AB139" s="19">
-        <f>IF($A139="","",ROUND(N139*Parametri!$C$6,2))</f>
+        <f>IF($A139="","",ROUND(ROUND(N139,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC139" s="19">
@@ -35769,7 +35769,7 @@
         <v/>
       </c>
       <c r="AB140" s="19">
-        <f>IF($A140="","",ROUND(N140*Parametri!$C$6,2))</f>
+        <f>IF($A140="","",ROUND(ROUND(N140,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC140" s="19">
@@ -35863,7 +35863,7 @@
         <v/>
       </c>
       <c r="AB141" s="19">
-        <f>IF($A141="","",ROUND(N141*Parametri!$C$6,2))</f>
+        <f>IF($A141="","",ROUND(ROUND(N141,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC141" s="19">
@@ -35957,7 +35957,7 @@
         <v/>
       </c>
       <c r="AB142" s="19">
-        <f>IF($A142="","",ROUND(N142*Parametri!$C$6,2))</f>
+        <f>IF($A142="","",ROUND(ROUND(N142,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC142" s="19">
@@ -36051,7 +36051,7 @@
         <v/>
       </c>
       <c r="AB143" s="19">
-        <f>IF($A143="","",ROUND(N143*Parametri!$C$6,2))</f>
+        <f>IF($A143="","",ROUND(ROUND(N143,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC143" s="19">
@@ -36145,7 +36145,7 @@
         <v/>
       </c>
       <c r="AB144" s="19">
-        <f>IF($A144="","",ROUND(N144*Parametri!$C$6,2))</f>
+        <f>IF($A144="","",ROUND(ROUND(N144,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC144" s="19">
@@ -36239,7 +36239,7 @@
         <v/>
       </c>
       <c r="AB145" s="19">
-        <f>IF($A145="","",ROUND(N145*Parametri!$C$6,2))</f>
+        <f>IF($A145="","",ROUND(ROUND(N145,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC145" s="19">
@@ -36333,7 +36333,7 @@
         <v/>
       </c>
       <c r="AB146" s="19">
-        <f>IF($A146="","",ROUND(N146*Parametri!$C$6,2))</f>
+        <f>IF($A146="","",ROUND(ROUND(N146,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC146" s="19">
@@ -36427,7 +36427,7 @@
         <v/>
       </c>
       <c r="AB147" s="19">
-        <f>IF($A147="","",ROUND(N147*Parametri!$C$6,2))</f>
+        <f>IF($A147="","",ROUND(ROUND(N147,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC147" s="19">
@@ -36521,7 +36521,7 @@
         <v/>
       </c>
       <c r="AB148" s="19">
-        <f>IF($A148="","",ROUND(N148*Parametri!$C$6,2))</f>
+        <f>IF($A148="","",ROUND(ROUND(N148,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC148" s="19">
@@ -36615,7 +36615,7 @@
         <v/>
       </c>
       <c r="AB149" s="19">
-        <f>IF($A149="","",ROUND(N149*Parametri!$C$6,2))</f>
+        <f>IF($A149="","",ROUND(ROUND(N149,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC149" s="19">
@@ -36709,7 +36709,7 @@
         <v/>
       </c>
       <c r="AB150" s="19">
-        <f>IF($A150="","",ROUND(N150*Parametri!$C$6,2))</f>
+        <f>IF($A150="","",ROUND(ROUND(N150,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC150" s="19">
@@ -36803,7 +36803,7 @@
         <v/>
       </c>
       <c r="AB151" s="19">
-        <f>IF($A151="","",ROUND(N151*Parametri!$C$6,2))</f>
+        <f>IF($A151="","",ROUND(ROUND(N151,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC151" s="19">
@@ -36897,7 +36897,7 @@
         <v/>
       </c>
       <c r="AB152" s="19">
-        <f>IF($A152="","",ROUND(N152*Parametri!$C$6,2))</f>
+        <f>IF($A152="","",ROUND(ROUND(N152,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC152" s="19">
@@ -36991,7 +36991,7 @@
         <v/>
       </c>
       <c r="AB153" s="19">
-        <f>IF($A153="","",ROUND(N153*Parametri!$C$6,2))</f>
+        <f>IF($A153="","",ROUND(ROUND(N153,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC153" s="19">
@@ -37085,7 +37085,7 @@
         <v/>
       </c>
       <c r="AB154" s="19">
-        <f>IF($A154="","",ROUND(N154*Parametri!$C$6,2))</f>
+        <f>IF($A154="","",ROUND(ROUND(N154,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC154" s="19">
@@ -37179,7 +37179,7 @@
         <v/>
       </c>
       <c r="AB155" s="19">
-        <f>IF($A155="","",ROUND(N155*Parametri!$C$6,2))</f>
+        <f>IF($A155="","",ROUND(ROUND(N155,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC155" s="19">
@@ -37273,7 +37273,7 @@
         <v/>
       </c>
       <c r="AB156" s="19">
-        <f>IF($A156="","",ROUND(N156*Parametri!$C$6,2))</f>
+        <f>IF($A156="","",ROUND(ROUND(N156,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC156" s="19">
@@ -37367,7 +37367,7 @@
         <v/>
       </c>
       <c r="AB157" s="19">
-        <f>IF($A157="","",ROUND(N157*Parametri!$C$6,2))</f>
+        <f>IF($A157="","",ROUND(ROUND(N157,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC157" s="19">
@@ -37461,7 +37461,7 @@
         <v/>
       </c>
       <c r="AB158" s="19">
-        <f>IF($A158="","",ROUND(N158*Parametri!$C$6,2))</f>
+        <f>IF($A158="","",ROUND(ROUND(N158,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC158" s="19">
@@ -37555,7 +37555,7 @@
         <v/>
       </c>
       <c r="AB159" s="19">
-        <f>IF($A159="","",ROUND(N159*Parametri!$C$6,2))</f>
+        <f>IF($A159="","",ROUND(ROUND(N159,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC159" s="19">
@@ -37649,7 +37649,7 @@
         <v/>
       </c>
       <c r="AB160" s="19">
-        <f>IF($A160="","",ROUND(N160*Parametri!$C$6,2))</f>
+        <f>IF($A160="","",ROUND(ROUND(N160,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC160" s="19">
@@ -37743,7 +37743,7 @@
         <v/>
       </c>
       <c r="AB161" s="19">
-        <f>IF($A161="","",ROUND(N161*Parametri!$C$6,2))</f>
+        <f>IF($A161="","",ROUND(ROUND(N161,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC161" s="19">
@@ -37837,7 +37837,7 @@
         <v/>
       </c>
       <c r="AB162" s="19">
-        <f>IF($A162="","",ROUND(N162*Parametri!$C$6,2))</f>
+        <f>IF($A162="","",ROUND(ROUND(N162,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC162" s="19">
@@ -37931,7 +37931,7 @@
         <v/>
       </c>
       <c r="AB163" s="19">
-        <f>IF($A163="","",ROUND(N163*Parametri!$C$6,2))</f>
+        <f>IF($A163="","",ROUND(ROUND(N163,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC163" s="19">
@@ -38025,7 +38025,7 @@
         <v/>
       </c>
       <c r="AB164" s="19">
-        <f>IF($A164="","",ROUND(N164*Parametri!$C$6,2))</f>
+        <f>IF($A164="","",ROUND(ROUND(N164,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC164" s="19">
@@ -38119,7 +38119,7 @@
         <v/>
       </c>
       <c r="AB165" s="19">
-        <f>IF($A165="","",ROUND(N165*Parametri!$C$6,2))</f>
+        <f>IF($A165="","",ROUND(ROUND(N165,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC165" s="19">
@@ -38213,7 +38213,7 @@
         <v/>
       </c>
       <c r="AB166" s="19">
-        <f>IF($A166="","",ROUND(N166*Parametri!$C$6,2))</f>
+        <f>IF($A166="","",ROUND(ROUND(N166,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC166" s="19">
@@ -38307,7 +38307,7 @@
         <v/>
       </c>
       <c r="AB167" s="19">
-        <f>IF($A167="","",ROUND(N167*Parametri!$C$6,2))</f>
+        <f>IF($A167="","",ROUND(ROUND(N167,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC167" s="19">
@@ -38401,7 +38401,7 @@
         <v/>
       </c>
       <c r="AB168" s="19">
-        <f>IF($A168="","",ROUND(N168*Parametri!$C$6,2))</f>
+        <f>IF($A168="","",ROUND(ROUND(N168,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC168" s="19">
@@ -38495,7 +38495,7 @@
         <v/>
       </c>
       <c r="AB169" s="19">
-        <f>IF($A169="","",ROUND(N169*Parametri!$C$6,2))</f>
+        <f>IF($A169="","",ROUND(ROUND(N169,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC169" s="19">
@@ -38589,7 +38589,7 @@
         <v/>
       </c>
       <c r="AB170" s="19">
-        <f>IF($A170="","",ROUND(N170*Parametri!$C$6,2))</f>
+        <f>IF($A170="","",ROUND(ROUND(N170,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC170" s="19">
@@ -38683,7 +38683,7 @@
         <v/>
       </c>
       <c r="AB171" s="19">
-        <f>IF($A171="","",ROUND(N171*Parametri!$C$6,2))</f>
+        <f>IF($A171="","",ROUND(ROUND(N171,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC171" s="19">
@@ -38777,7 +38777,7 @@
         <v/>
       </c>
       <c r="AB172" s="19">
-        <f>IF($A172="","",ROUND(N172*Parametri!$C$6,2))</f>
+        <f>IF($A172="","",ROUND(ROUND(N172,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC172" s="19">
@@ -38871,7 +38871,7 @@
         <v/>
       </c>
       <c r="AB173" s="19">
-        <f>IF($A173="","",ROUND(N173*Parametri!$C$6,2))</f>
+        <f>IF($A173="","",ROUND(ROUND(N173,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC173" s="19">
@@ -38965,7 +38965,7 @@
         <v/>
       </c>
       <c r="AB174" s="19">
-        <f>IF($A174="","",ROUND(N174*Parametri!$C$6,2))</f>
+        <f>IF($A174="","",ROUND(ROUND(N174,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC174" s="19">
@@ -39059,7 +39059,7 @@
         <v/>
       </c>
       <c r="AB175" s="19">
-        <f>IF($A175="","",ROUND(N175*Parametri!$C$6,2))</f>
+        <f>IF($A175="","",ROUND(ROUND(N175,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC175" s="19">
@@ -39153,7 +39153,7 @@
         <v/>
       </c>
       <c r="AB176" s="19">
-        <f>IF($A176="","",ROUND(N176*Parametri!$C$6,2))</f>
+        <f>IF($A176="","",ROUND(ROUND(N176,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC176" s="19">
@@ -39247,7 +39247,7 @@
         <v/>
       </c>
       <c r="AB177" s="19">
-        <f>IF($A177="","",ROUND(N177*Parametri!$C$6,2))</f>
+        <f>IF($A177="","",ROUND(ROUND(N177,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC177" s="19">
@@ -39341,7 +39341,7 @@
         <v/>
       </c>
       <c r="AB178" s="19">
-        <f>IF($A178="","",ROUND(N178*Parametri!$C$6,2))</f>
+        <f>IF($A178="","",ROUND(ROUND(N178,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC178" s="19">
@@ -39435,7 +39435,7 @@
         <v/>
       </c>
       <c r="AB179" s="19">
-        <f>IF($A179="","",ROUND(N179*Parametri!$C$6,2))</f>
+        <f>IF($A179="","",ROUND(ROUND(N179,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC179" s="19">
@@ -39529,7 +39529,7 @@
         <v/>
       </c>
       <c r="AB180" s="19">
-        <f>IF($A180="","",ROUND(N180*Parametri!$C$6,2))</f>
+        <f>IF($A180="","",ROUND(ROUND(N180,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC180" s="19">
@@ -39623,7 +39623,7 @@
         <v/>
       </c>
       <c r="AB181" s="19">
-        <f>IF($A181="","",ROUND(N181*Parametri!$C$6,2))</f>
+        <f>IF($A181="","",ROUND(ROUND(N181,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC181" s="19">
@@ -39717,7 +39717,7 @@
         <v/>
       </c>
       <c r="AB182" s="19">
-        <f>IF($A182="","",ROUND(N182*Parametri!$C$6,2))</f>
+        <f>IF($A182="","",ROUND(ROUND(N182,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC182" s="19">
@@ -39811,7 +39811,7 @@
         <v/>
       </c>
       <c r="AB183" s="19">
-        <f>IF($A183="","",ROUND(N183*Parametri!$C$6,2))</f>
+        <f>IF($A183="","",ROUND(ROUND(N183,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC183" s="19">
@@ -39905,7 +39905,7 @@
         <v/>
       </c>
       <c r="AB184" s="19">
-        <f>IF($A184="","",ROUND(N184*Parametri!$C$6,2))</f>
+        <f>IF($A184="","",ROUND(ROUND(N184,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC184" s="19">
@@ -39999,7 +39999,7 @@
         <v/>
       </c>
       <c r="AB185" s="19">
-        <f>IF($A185="","",ROUND(N185*Parametri!$C$6,2))</f>
+        <f>IF($A185="","",ROUND(ROUND(N185,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC185" s="19">
@@ -40093,7 +40093,7 @@
         <v/>
       </c>
       <c r="AB186" s="19">
-        <f>IF($A186="","",ROUND(N186*Parametri!$C$6,2))</f>
+        <f>IF($A186="","",ROUND(ROUND(N186,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC186" s="19">
@@ -40187,7 +40187,7 @@
         <v/>
       </c>
       <c r="AB187" s="19">
-        <f>IF($A187="","",ROUND(N187*Parametri!$C$6,2))</f>
+        <f>IF($A187="","",ROUND(ROUND(N187,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC187" s="19">
@@ -40281,7 +40281,7 @@
         <v/>
       </c>
       <c r="AB188" s="19">
-        <f>IF($A188="","",ROUND(N188*Parametri!$C$6,2))</f>
+        <f>IF($A188="","",ROUND(ROUND(N188,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC188" s="19">
@@ -40375,7 +40375,7 @@
         <v/>
       </c>
       <c r="AB189" s="19">
-        <f>IF($A189="","",ROUND(N189*Parametri!$C$6,2))</f>
+        <f>IF($A189="","",ROUND(ROUND(N189,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC189" s="19">
@@ -40469,7 +40469,7 @@
         <v/>
       </c>
       <c r="AB190" s="19">
-        <f>IF($A190="","",ROUND(N190*Parametri!$C$6,2))</f>
+        <f>IF($A190="","",ROUND(ROUND(N190,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC190" s="19">
@@ -40563,7 +40563,7 @@
         <v/>
       </c>
       <c r="AB191" s="19">
-        <f>IF($A191="","",ROUND(N191*Parametri!$C$6,2))</f>
+        <f>IF($A191="","",ROUND(ROUND(N191,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC191" s="19">
@@ -40657,7 +40657,7 @@
         <v/>
       </c>
       <c r="AB192" s="19">
-        <f>IF($A192="","",ROUND(N192*Parametri!$C$6,2))</f>
+        <f>IF($A192="","",ROUND(ROUND(N192,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC192" s="19">
@@ -40751,7 +40751,7 @@
         <v/>
       </c>
       <c r="AB193" s="19">
-        <f>IF($A193="","",ROUND(N193*Parametri!$C$6,2))</f>
+        <f>IF($A193="","",ROUND(ROUND(N193,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC193" s="19">
@@ -40845,7 +40845,7 @@
         <v/>
       </c>
       <c r="AB194" s="19">
-        <f>IF($A194="","",ROUND(N194*Parametri!$C$6,2))</f>
+        <f>IF($A194="","",ROUND(ROUND(N194,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC194" s="19">
@@ -40939,7 +40939,7 @@
         <v/>
       </c>
       <c r="AB195" s="19">
-        <f>IF($A195="","",ROUND(N195*Parametri!$C$6,2))</f>
+        <f>IF($A195="","",ROUND(ROUND(N195,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC195" s="19">
@@ -41033,7 +41033,7 @@
         <v/>
       </c>
       <c r="AB196" s="19">
-        <f>IF($A196="","",ROUND(N196*Parametri!$C$6,2))</f>
+        <f>IF($A196="","",ROUND(ROUND(N196,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC196" s="19">
@@ -41127,7 +41127,7 @@
         <v/>
       </c>
       <c r="AB197" s="19">
-        <f>IF($A197="","",ROUND(N197*Parametri!$C$6,2))</f>
+        <f>IF($A197="","",ROUND(ROUND(N197,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC197" s="19">
@@ -41221,7 +41221,7 @@
         <v/>
       </c>
       <c r="AB198" s="19">
-        <f>IF($A198="","",ROUND(N198*Parametri!$C$6,2))</f>
+        <f>IF($A198="","",ROUND(ROUND(N198,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC198" s="19">
@@ -41315,7 +41315,7 @@
         <v/>
       </c>
       <c r="AB199" s="19">
-        <f>IF($A199="","",ROUND(N199*Parametri!$C$6,2))</f>
+        <f>IF($A199="","",ROUND(ROUND(N199,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC199" s="19">
@@ -41409,7 +41409,7 @@
         <v/>
       </c>
       <c r="AB200" s="19">
-        <f>IF($A200="","",ROUND(N200*Parametri!$C$6,2))</f>
+        <f>IF($A200="","",ROUND(ROUND(N200,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC200" s="19">
@@ -41503,7 +41503,7 @@
         <v/>
       </c>
       <c r="AB201" s="19">
-        <f>IF($A201="","",ROUND(N201*Parametri!$C$6,2))</f>
+        <f>IF($A201="","",ROUND(ROUND(N201,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC201" s="19">
@@ -41597,7 +41597,7 @@
         <v/>
       </c>
       <c r="AB202" s="19">
-        <f>IF($A202="","",ROUND(N202*Parametri!$C$6,2))</f>
+        <f>IF($A202="","",ROUND(ROUND(N202,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC202" s="19">
@@ -41691,7 +41691,7 @@
         <v/>
       </c>
       <c r="AB203" s="19">
-        <f>IF($A203="","",ROUND(N203*Parametri!$C$6,2))</f>
+        <f>IF($A203="","",ROUND(ROUND(N203,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC203" s="19">
@@ -41785,7 +41785,7 @@
         <v/>
       </c>
       <c r="AB204" s="19">
-        <f>IF($A204="","",ROUND(N204*Parametri!$C$6,2))</f>
+        <f>IF($A204="","",ROUND(ROUND(N204,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC204" s="19">
@@ -41879,7 +41879,7 @@
         <v/>
       </c>
       <c r="AB205" s="19">
-        <f>IF($A205="","",ROUND(N205*Parametri!$C$6,2))</f>
+        <f>IF($A205="","",ROUND(ROUND(N205,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC205" s="19">
@@ -41973,7 +41973,7 @@
         <v/>
       </c>
       <c r="AB206" s="19">
-        <f>IF($A206="","",ROUND(N206*Parametri!$C$6,2))</f>
+        <f>IF($A206="","",ROUND(ROUND(N206,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC206" s="19">
@@ -42067,7 +42067,7 @@
         <v/>
       </c>
       <c r="AB207" s="19">
-        <f>IF($A207="","",ROUND(N207*Parametri!$C$6,2))</f>
+        <f>IF($A207="","",ROUND(ROUND(N207,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC207" s="19">
@@ -42161,7 +42161,7 @@
         <v/>
       </c>
       <c r="AB208" s="19">
-        <f>IF($A208="","",ROUND(N208*Parametri!$C$6,2))</f>
+        <f>IF($A208="","",ROUND(ROUND(N208,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC208" s="19">
@@ -42255,7 +42255,7 @@
         <v/>
       </c>
       <c r="AB209" s="19">
-        <f>IF($A209="","",ROUND(N209*Parametri!$C$6,2))</f>
+        <f>IF($A209="","",ROUND(ROUND(N209,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC209" s="19">
@@ -42349,7 +42349,7 @@
         <v/>
       </c>
       <c r="AB210" s="19">
-        <f>IF($A210="","",ROUND(N210*Parametri!$C$6,2))</f>
+        <f>IF($A210="","",ROUND(ROUND(N210,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC210" s="19">
@@ -42443,7 +42443,7 @@
         <v/>
       </c>
       <c r="AB211" s="19">
-        <f>IF($A211="","",ROUND(N211*Parametri!$C$6,2))</f>
+        <f>IF($A211="","",ROUND(ROUND(N211,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC211" s="19">
@@ -42537,7 +42537,7 @@
         <v/>
       </c>
       <c r="AB212" s="19">
-        <f>IF($A212="","",ROUND(N212*Parametri!$C$6,2))</f>
+        <f>IF($A212="","",ROUND(ROUND(N212,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC212" s="19">
@@ -42631,7 +42631,7 @@
         <v/>
       </c>
       <c r="AB213" s="19">
-        <f>IF($A213="","",ROUND(N213*Parametri!$C$6,2))</f>
+        <f>IF($A213="","",ROUND(ROUND(N213,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC213" s="19">
@@ -42725,7 +42725,7 @@
         <v/>
       </c>
       <c r="AB214" s="19">
-        <f>IF($A214="","",ROUND(N214*Parametri!$C$6,2))</f>
+        <f>IF($A214="","",ROUND(ROUND(N214,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC214" s="19">
@@ -42819,7 +42819,7 @@
         <v/>
       </c>
       <c r="AB215" s="19">
-        <f>IF($A215="","",ROUND(N215*Parametri!$C$6,2))</f>
+        <f>IF($A215="","",ROUND(ROUND(N215,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC215" s="19">
@@ -42913,7 +42913,7 @@
         <v/>
       </c>
       <c r="AB216" s="19">
-        <f>IF($A216="","",ROUND(N216*Parametri!$C$6,2))</f>
+        <f>IF($A216="","",ROUND(ROUND(N216,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC216" s="19">
@@ -43007,7 +43007,7 @@
         <v/>
       </c>
       <c r="AB217" s="19">
-        <f>IF($A217="","",ROUND(N217*Parametri!$C$6,2))</f>
+        <f>IF($A217="","",ROUND(ROUND(N217,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC217" s="19">
@@ -43101,7 +43101,7 @@
         <v/>
       </c>
       <c r="AB218" s="19">
-        <f>IF($A218="","",ROUND(N218*Parametri!$C$6,2))</f>
+        <f>IF($A218="","",ROUND(ROUND(N218,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC218" s="19">
@@ -43195,7 +43195,7 @@
         <v/>
       </c>
       <c r="AB219" s="19">
-        <f>IF($A219="","",ROUND(N219*Parametri!$C$6,2))</f>
+        <f>IF($A219="","",ROUND(ROUND(N219,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC219" s="19">
@@ -43289,7 +43289,7 @@
         <v/>
       </c>
       <c r="AB220" s="19">
-        <f>IF($A220="","",ROUND(N220*Parametri!$C$6,2))</f>
+        <f>IF($A220="","",ROUND(ROUND(N220,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC220" s="19">
@@ -43383,7 +43383,7 @@
         <v/>
       </c>
       <c r="AB221" s="19">
-        <f>IF($A221="","",ROUND(N221*Parametri!$C$6,2))</f>
+        <f>IF($A221="","",ROUND(ROUND(N221,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC221" s="19">
@@ -43477,7 +43477,7 @@
         <v/>
       </c>
       <c r="AB222" s="19">
-        <f>IF($A222="","",ROUND(N222*Parametri!$C$6,2))</f>
+        <f>IF($A222="","",ROUND(ROUND(N222,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC222" s="19">
@@ -43571,7 +43571,7 @@
         <v/>
       </c>
       <c r="AB223" s="19">
-        <f>IF($A223="","",ROUND(N223*Parametri!$C$6,2))</f>
+        <f>IF($A223="","",ROUND(ROUND(N223,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC223" s="19">
@@ -43665,7 +43665,7 @@
         <v/>
       </c>
       <c r="AB224" s="19">
-        <f>IF($A224="","",ROUND(N224*Parametri!$C$6,2))</f>
+        <f>IF($A224="","",ROUND(ROUND(N224,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC224" s="19">
@@ -43759,7 +43759,7 @@
         <v/>
       </c>
       <c r="AB225" s="19">
-        <f>IF($A225="","",ROUND(N225*Parametri!$C$6,2))</f>
+        <f>IF($A225="","",ROUND(ROUND(N225,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC225" s="19">
@@ -43853,7 +43853,7 @@
         <v/>
       </c>
       <c r="AB226" s="19">
-        <f>IF($A226="","",ROUND(N226*Parametri!$C$6,2))</f>
+        <f>IF($A226="","",ROUND(ROUND(N226,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC226" s="19">
@@ -43947,7 +43947,7 @@
         <v/>
       </c>
       <c r="AB227" s="19">
-        <f>IF($A227="","",ROUND(N227*Parametri!$C$6,2))</f>
+        <f>IF($A227="","",ROUND(ROUND(N227,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC227" s="19">
@@ -44041,7 +44041,7 @@
         <v/>
       </c>
       <c r="AB228" s="19">
-        <f>IF($A228="","",ROUND(N228*Parametri!$C$6,2))</f>
+        <f>IF($A228="","",ROUND(ROUND(N228,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC228" s="19">
@@ -44135,7 +44135,7 @@
         <v/>
       </c>
       <c r="AB229" s="19">
-        <f>IF($A229="","",ROUND(N229*Parametri!$C$6,2))</f>
+        <f>IF($A229="","",ROUND(ROUND(N229,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC229" s="19">
@@ -44229,7 +44229,7 @@
         <v/>
       </c>
       <c r="AB230" s="19">
-        <f>IF($A230="","",ROUND(N230*Parametri!$C$6,2))</f>
+        <f>IF($A230="","",ROUND(ROUND(N230,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC230" s="19">
@@ -44323,7 +44323,7 @@
         <v/>
       </c>
       <c r="AB231" s="19">
-        <f>IF($A231="","",ROUND(N231*Parametri!$C$6,2))</f>
+        <f>IF($A231="","",ROUND(ROUND(N231,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC231" s="19">
@@ -44417,7 +44417,7 @@
         <v/>
       </c>
       <c r="AB232" s="19">
-        <f>IF($A232="","",ROUND(N232*Parametri!$C$6,2))</f>
+        <f>IF($A232="","",ROUND(ROUND(N232,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC232" s="19">
@@ -44511,7 +44511,7 @@
         <v/>
       </c>
       <c r="AB233" s="19">
-        <f>IF($A233="","",ROUND(N233*Parametri!$C$6,2))</f>
+        <f>IF($A233="","",ROUND(ROUND(N233,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC233" s="19">
@@ -44605,7 +44605,7 @@
         <v/>
       </c>
       <c r="AB234" s="19">
-        <f>IF($A234="","",ROUND(N234*Parametri!$C$6,2))</f>
+        <f>IF($A234="","",ROUND(ROUND(N234,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC234" s="19">
@@ -44699,7 +44699,7 @@
         <v/>
       </c>
       <c r="AB235" s="19">
-        <f>IF($A235="","",ROUND(N235*Parametri!$C$6,2))</f>
+        <f>IF($A235="","",ROUND(ROUND(N235,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC235" s="19">
@@ -44793,7 +44793,7 @@
         <v/>
       </c>
       <c r="AB236" s="19">
-        <f>IF($A236="","",ROUND(N236*Parametri!$C$6,2))</f>
+        <f>IF($A236="","",ROUND(ROUND(N236,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC236" s="19">
@@ -44887,7 +44887,7 @@
         <v/>
       </c>
       <c r="AB237" s="19">
-        <f>IF($A237="","",ROUND(N237*Parametri!$C$6,2))</f>
+        <f>IF($A237="","",ROUND(ROUND(N237,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC237" s="19">
@@ -44981,7 +44981,7 @@
         <v/>
       </c>
       <c r="AB238" s="19">
-        <f>IF($A238="","",ROUND(N238*Parametri!$C$6,2))</f>
+        <f>IF($A238="","",ROUND(ROUND(N238,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC238" s="19">
@@ -45075,7 +45075,7 @@
         <v/>
       </c>
       <c r="AB239" s="19">
-        <f>IF($A239="","",ROUND(N239*Parametri!$C$6,2))</f>
+        <f>IF($A239="","",ROUND(ROUND(N239,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC239" s="19">
@@ -45169,7 +45169,7 @@
         <v/>
       </c>
       <c r="AB240" s="19">
-        <f>IF($A240="","",ROUND(N240*Parametri!$C$6,2))</f>
+        <f>IF($A240="","",ROUND(ROUND(N240,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC240" s="19">
@@ -45263,7 +45263,7 @@
         <v/>
       </c>
       <c r="AB241" s="19">
-        <f>IF($A241="","",ROUND(N241*Parametri!$C$6,2))</f>
+        <f>IF($A241="","",ROUND(ROUND(N241,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC241" s="19">
@@ -45357,7 +45357,7 @@
         <v/>
       </c>
       <c r="AB242" s="19">
-        <f>IF($A242="","",ROUND(N242*Parametri!$C$6,2))</f>
+        <f>IF($A242="","",ROUND(ROUND(N242,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC242" s="19">
@@ -45451,7 +45451,7 @@
         <v/>
       </c>
       <c r="AB243" s="19">
-        <f>IF($A243="","",ROUND(N243*Parametri!$C$6,2))</f>
+        <f>IF($A243="","",ROUND(ROUND(N243,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC243" s="19">
@@ -45545,7 +45545,7 @@
         <v/>
       </c>
       <c r="AB244" s="19">
-        <f>IF($A244="","",ROUND(N244*Parametri!$C$6,2))</f>
+        <f>IF($A244="","",ROUND(ROUND(N244,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC244" s="19">
@@ -45639,7 +45639,7 @@
         <v/>
       </c>
       <c r="AB245" s="19">
-        <f>IF($A245="","",ROUND(N245*Parametri!$C$6,2))</f>
+        <f>IF($A245="","",ROUND(ROUND(N245,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC245" s="19">
@@ -45733,7 +45733,7 @@
         <v/>
       </c>
       <c r="AB246" s="19">
-        <f>IF($A246="","",ROUND(N246*Parametri!$C$6,2))</f>
+        <f>IF($A246="","",ROUND(ROUND(N246,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC246" s="19">
@@ -45827,7 +45827,7 @@
         <v/>
       </c>
       <c r="AB247" s="19">
-        <f>IF($A247="","",ROUND(N247*Parametri!$C$6,2))</f>
+        <f>IF($A247="","",ROUND(ROUND(N247,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC247" s="19">
@@ -45921,7 +45921,7 @@
         <v/>
       </c>
       <c r="AB248" s="19">
-        <f>IF($A248="","",ROUND(N248*Parametri!$C$6,2))</f>
+        <f>IF($A248="","",ROUND(ROUND(N248,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC248" s="19">
@@ -46015,7 +46015,7 @@
         <v/>
       </c>
       <c r="AB249" s="19">
-        <f>IF($A249="","",ROUND(N249*Parametri!$C$6,2))</f>
+        <f>IF($A249="","",ROUND(ROUND(N249,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC249" s="19">
@@ -46109,7 +46109,7 @@
         <v/>
       </c>
       <c r="AB250" s="19">
-        <f>IF($A250="","",ROUND(N250*Parametri!$C$6,2))</f>
+        <f>IF($A250="","",ROUND(ROUND(N250,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC250" s="19">
@@ -46203,7 +46203,7 @@
         <v/>
       </c>
       <c r="AB251" s="19">
-        <f>IF($A251="","",ROUND(N251*Parametri!$C$6,2))</f>
+        <f>IF($A251="","",ROUND(ROUND(N251,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC251" s="19">
@@ -46297,7 +46297,7 @@
         <v/>
       </c>
       <c r="AB252" s="19">
-        <f>IF($A252="","",ROUND(N252*Parametri!$C$6,2))</f>
+        <f>IF($A252="","",ROUND(ROUND(N252,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC252" s="19">
@@ -46391,7 +46391,7 @@
         <v/>
       </c>
       <c r="AB253" s="19">
-        <f>IF($A253="","",ROUND(N253*Parametri!$C$6,2))</f>
+        <f>IF($A253="","",ROUND(ROUND(N253,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC253" s="19">
@@ -46485,7 +46485,7 @@
         <v/>
       </c>
       <c r="AB254" s="19">
-        <f>IF($A254="","",ROUND(N254*Parametri!$C$6,2))</f>
+        <f>IF($A254="","",ROUND(ROUND(N254,0)*Parametri!$C$6,2))</f>
         <v/>
       </c>
       <c r="AC254" s="19">
@@ -46663,7 +46663,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>1310.02</v>
+        <v>1310</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>6.686</v>
@@ -46695,7 +46695,7 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1537.93</v>
+        <v>1537.91</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>2.8031</v>
@@ -46727,7 +46727,7 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>1499.61</v>
+        <v>1499.58</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>31.82</v>
@@ -46759,7 +46759,7 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>1577.94</v>
+        <v>1577.97</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>15.0127</v>
@@ -46791,7 +46791,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>1205.95</v>
+        <v>1205.98</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>21.1311</v>
@@ -46855,7 +46855,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>1970.3</v>
+        <v>1970.29</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>17.3519</v>
@@ -46887,7 +46887,7 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>1513.96</v>
+        <v>1513.95</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>11.1243</v>
@@ -46919,7 +46919,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1309.15</v>
+        <v>1309.17</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>20.7886</v>
@@ -46951,7 +46951,7 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>1179.86</v>
+        <v>1179.87</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>14.0704</v>
@@ -46983,7 +46983,7 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>1604.78</v>
+        <v>1604.76</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>25.8977</v>
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>1195.1</v>
+        <v>1195.09</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>21.911</v>
@@ -47047,7 +47047,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>1150.97</v>
+        <v>1150.95</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>9.379899999999999</v>
@@ -47079,7 +47079,7 @@
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>1522.71</v>
+        <v>1522.73</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>13.7701</v>
@@ -47111,7 +47111,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1304.5</v>
+        <v>1304.51</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>27.4397</v>
@@ -47175,7 +47175,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1079.08</v>
+        <v>1079.1</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>25.4459</v>
@@ -47207,7 +47207,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>1551.65</v>
+        <v>1551.63</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>12.3163</v>
@@ -47239,7 +47239,7 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1752.11</v>
+        <v>1752.09</v>
       </c>
       <c r="D23" s="18" t="n">
         <v>20.113</v>
@@ -47271,7 +47271,7 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>1969.58</v>
+        <v>1969.57</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>7.9673</v>
@@ -47303,7 +47303,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1480.56</v>
+        <v>1480.58</v>
       </c>
       <c r="D25" s="18" t="n">
         <v>22.9062</v>
@@ -47335,7 +47335,7 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1499.7</v>
+        <v>1499.69</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>17.0036</v>
@@ -47367,7 +47367,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1830.03</v>
+        <v>1830.01</v>
       </c>
       <c r="D27" s="18" t="n">
         <v>20.5321</v>
@@ -47399,7 +47399,7 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1315.81</v>
+        <v>1315.78</v>
       </c>
       <c r="D28" s="18" t="n">
         <v>13.5197</v>
@@ -47431,7 +47431,7 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1131.9</v>
+        <v>1131.92</v>
       </c>
       <c r="D29" s="18" t="n">
         <v>16.3948</v>
@@ -47463,7 +47463,7 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1914.26</v>
+        <v>1914.25</v>
       </c>
       <c r="D30" s="18" t="n">
         <v>17.7804</v>
@@ -47495,7 +47495,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1279.2</v>
+        <v>1279.22</v>
       </c>
       <c r="D31" s="18" t="n">
         <v>29.1882</v>
@@ -47559,7 +47559,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>759.13</v>
+        <v>759.11</v>
       </c>
       <c r="D33" s="18" t="n">
         <v>8.758699999999999</v>
@@ -47591,7 +47591,7 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>1119.26</v>
+        <v>1119.25</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>11.3863</v>
@@ -47623,7 +47623,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>819.16</v>
+        <v>819.17</v>
       </c>
       <c r="D35" s="18" t="n">
         <v>2.7543</v>
@@ -47655,7 +47655,7 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>1383.16</v>
+        <v>1383.19</v>
       </c>
       <c r="D36" s="18" t="n">
         <v>21.2095</v>
@@ -47687,7 +47687,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1677.39</v>
+        <v>1677.43</v>
       </c>
       <c r="D37" s="18" t="n">
         <v>10.2963</v>
@@ -47719,7 +47719,7 @@
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="D38" s="18" t="n">
         <v>11.2602</v>
@@ -47751,7 +47751,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>849.33</v>
+        <v>849.35</v>
       </c>
       <c r="D39" s="18" t="n">
         <v>24.4417</v>
@@ -47783,7 +47783,7 @@
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1188.7</v>
+        <v>1188.68</v>
       </c>
       <c r="D40" s="18" t="n">
         <v>16.8552</v>
@@ -47815,7 +47815,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1169.83</v>
+        <v>1169.81</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>7.8266</v>
@@ -47847,7 +47847,7 @@
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>1236.69</v>
+        <v>1236.67</v>
       </c>
       <c r="D42" s="18" t="n">
         <v>2.1671</v>
@@ -47911,7 +47911,7 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>1461.07</v>
+        <v>1461.09</v>
       </c>
       <c r="D44" s="18" t="n">
         <v>12.7885</v>
@@ -47943,7 +47943,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>1937.71</v>
+        <v>1937.7</v>
       </c>
       <c r="D45" s="18" t="n">
         <v>9.230600000000001</v>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>1393.73</v>
+        <v>1393.7</v>
       </c>
       <c r="D46" s="18" t="n">
         <v>19.0842</v>
@@ -48007,7 +48007,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>1367.75</v>
+        <v>1367.72</v>
       </c>
       <c r="D47" s="18" t="n">
         <v>19.9635</v>
@@ -48039,7 +48039,7 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1899.47</v>
+        <v>1899.48</v>
       </c>
       <c r="D48" s="18" t="n">
         <v>4.6458</v>
@@ -48071,7 +48071,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>704.26</v>
+        <v>704.24</v>
       </c>
       <c r="D49" s="18" t="n">
         <v>13.5616</v>
@@ -48135,7 +48135,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1889.4</v>
+        <v>1889.41</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>5.2692</v>
@@ -48167,7 +48167,7 @@
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>823.27</v>
+        <v>823.28</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>21.1473</v>
@@ -48199,7 +48199,7 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>2009.9</v>
+        <v>2009.89</v>
       </c>
       <c r="D53" s="18" t="n">
         <v>11.5295</v>
@@ -48263,7 +48263,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>1274.4</v>
+        <v>1274.38</v>
       </c>
       <c r="D55" s="18" t="n">
         <v>12.3157</v>
@@ -48295,7 +48295,7 @@
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>1413.2</v>
+        <v>1413.18</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>16.9202</v>
@@ -48359,7 +48359,7 @@
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>1577.94</v>
+        <v>1577.97</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>11.5435</v>
@@ -48391,7 +48391,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>1458.85</v>
+        <v>1458.84</v>
       </c>
       <c r="D59" s="18" t="n">
         <v>12.2349</v>
@@ -48455,7 +48455,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>1225.44</v>
+        <v>1225.47</v>
       </c>
       <c r="D61" s="18" t="n">
         <v>13.178</v>
@@ -48519,7 +48519,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1560.68</v>
+        <v>1560.67</v>
       </c>
       <c r="D63" s="18" t="n">
         <v>2.6968</v>
@@ -48551,7 +48551,7 @@
         </is>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1366.85</v>
+        <v>1366.87</v>
       </c>
       <c r="D64" s="18" t="n">
         <v>17.175</v>
@@ -48583,7 +48583,7 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="D65" s="18" t="n">
         <v>14.4707</v>
@@ -48615,7 +48615,7 @@
         </is>
       </c>
       <c r="C66" s="17" t="n">
-        <v>1435.1</v>
+        <v>1435.12</v>
       </c>
       <c r="D66" s="18" t="n">
         <v>26.4321</v>
@@ -48679,7 +48679,7 @@
         </is>
       </c>
       <c r="C68" s="17" t="n">
-        <v>1287.04</v>
+        <v>1287.07</v>
       </c>
       <c r="D68" s="18" t="n">
         <v>16.9725</v>
@@ -48711,7 +48711,7 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>1432.48</v>
+        <v>1432.5</v>
       </c>
       <c r="D69" s="18" t="n">
         <v>5.0881</v>
@@ -48743,7 +48743,7 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1692.82</v>
+        <v>1692.84</v>
       </c>
       <c r="D70" s="18" t="n">
         <v>9.1441</v>
@@ -48775,7 +48775,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1177.93</v>
+        <v>1177.95</v>
       </c>
       <c r="D71" s="18" t="n">
         <v>5.2953</v>
@@ -48807,7 +48807,7 @@
         </is>
       </c>
       <c r="C72" s="17" t="n">
-        <v>1461.94</v>
+        <v>1461.91</v>
       </c>
       <c r="D72" s="18" t="n">
         <v>9.084199999999999</v>
@@ -48839,7 +48839,7 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1542.42</v>
+        <v>1542.4</v>
       </c>
       <c r="D73" s="18" t="n">
         <v>12.9473</v>
@@ -48871,7 +48871,7 @@
         </is>
       </c>
       <c r="C74" s="17" t="n">
-        <v>1343.07</v>
+        <v>1343.04</v>
       </c>
       <c r="D74" s="18" t="n">
         <v>11.9406</v>
@@ -48903,7 +48903,7 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>904.86</v>
+        <v>904.87</v>
       </c>
       <c r="D75" s="18" t="n">
         <v>17.2249</v>
@@ -48935,7 +48935,7 @@
         </is>
       </c>
       <c r="C76" s="17" t="n">
-        <v>1480.56</v>
+        <v>1480.58</v>
       </c>
       <c r="D76" s="18" t="n">
         <v>9.324199999999999</v>
@@ -48967,7 +48967,7 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>1577.94</v>
+        <v>1577.97</v>
       </c>
       <c r="D77" s="18" t="n">
         <v>19.626</v>
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="C78" s="17" t="n">
-        <v>1541.57</v>
+        <v>1541.58</v>
       </c>
       <c r="D78" s="18" t="n">
         <v>7.124</v>
@@ -49031,7 +49031,7 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>1450.23</v>
+        <v>1450.21</v>
       </c>
       <c r="D79" s="18" t="n">
         <v>12.0726</v>
@@ -49063,7 +49063,7 @@
         </is>
       </c>
       <c r="C80" s="17" t="n">
-        <v>1079.08</v>
+        <v>1079.1</v>
       </c>
       <c r="D80" s="18" t="n">
         <v>2.3027</v>
@@ -49095,7 +49095,7 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>1536.96</v>
+        <v>1536.97</v>
       </c>
       <c r="D81" s="18" t="n">
         <v>9.803699999999999</v>
@@ -49127,7 +49127,7 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1970.3</v>
+        <v>1970.29</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>12.1962</v>
@@ -49159,7 +49159,7 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>1546.42</v>
+        <v>1546.41</v>
       </c>
       <c r="D83" s="18" t="n">
         <v>11.8658</v>
@@ -49191,7 +49191,7 @@
         </is>
       </c>
       <c r="C84" s="17" t="n">
-        <v>1234.08</v>
+        <v>1234.05</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>26.1772</v>
@@ -49223,7 +49223,7 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>1421.69</v>
+        <v>1421.67</v>
       </c>
       <c r="D85" s="18" t="n">
         <v>22.5457</v>
@@ -49287,7 +49287,7 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>1383.16</v>
+        <v>1383.19</v>
       </c>
       <c r="D87" s="18" t="n">
         <v>19.9734</v>
@@ -49319,7 +49319,7 @@
         </is>
       </c>
       <c r="C88" s="17" t="n">
-        <v>1553.26</v>
+        <v>1553.28</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>15.8011</v>
@@ -49351,7 +49351,7 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>815.28</v>
+        <v>815.24</v>
       </c>
       <c r="D89" s="18" t="n">
         <v>10.656</v>
@@ -49383,7 +49383,7 @@
         </is>
       </c>
       <c r="C90" s="17" t="n">
-        <v>1383.16</v>
+        <v>1383.19</v>
       </c>
       <c r="D90" s="18" t="n">
         <v>11.8565</v>
@@ -49415,7 +49415,7 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>1100.33</v>
+        <v>1100.34</v>
       </c>
       <c r="D91" s="18" t="n">
         <v>18.0034</v>
@@ -49447,7 +49447,7 @@
         </is>
       </c>
       <c r="C92" s="17" t="n">
-        <v>802.01</v>
+        <v>802.03</v>
       </c>
       <c r="D92" s="18" t="n">
         <v>11.1017</v>
@@ -49479,7 +49479,7 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>1103.06</v>
+        <v>1103.08</v>
       </c>
       <c r="D93" s="18" t="n">
         <v>19.4093</v>
@@ -49511,7 +49511,7 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1752.11</v>
+        <v>1752.09</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>5.922</v>
@@ -49575,7 +49575,7 @@
         </is>
       </c>
       <c r="C96" s="17" t="n">
-        <v>1387.82</v>
+        <v>1387.78</v>
       </c>
       <c r="D96" s="18" t="n">
         <v>29.6456</v>
@@ -49607,7 +49607,7 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>1528.21</v>
+        <v>1528.2</v>
       </c>
       <c r="D97" s="18" t="n">
         <v>20.2632</v>
@@ -49767,7 +49767,7 @@
         </is>
       </c>
       <c r="C102" s="17" t="n">
-        <v>1617.68</v>
+        <v>1617.66</v>
       </c>
       <c r="D102" s="18" t="n">
         <v>20.0905</v>
@@ -49799,7 +49799,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1467.14</v>
+        <v>1467.12</v>
       </c>
       <c r="D103" s="18" t="n">
         <v>12.4172</v>
@@ -49831,7 +49831,7 @@
         </is>
       </c>
       <c r="C104" s="17" t="n">
-        <v>1187.99</v>
+        <v>1187.98</v>
       </c>
       <c r="D104" s="18" t="n">
         <v>9.988799999999999</v>
@@ -49863,7 +49863,7 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1394.11</v>
+        <v>1394.13</v>
       </c>
       <c r="D105" s="18" t="n">
         <v>16.2724</v>
@@ -49927,7 +49927,7 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1336.08</v>
+        <v>1336.06</v>
       </c>
       <c r="D107" s="18" t="n">
         <v>18.5598</v>
@@ -50023,7 +50023,7 @@
         </is>
       </c>
       <c r="C110" s="17" t="n">
-        <v>1423.41</v>
+        <v>1423.42</v>
       </c>
       <c r="D110" s="18" t="n">
         <v>23.3743</v>
@@ -50087,7 +50087,7 @@
         </is>
       </c>
       <c r="C112" s="17" t="n">
-        <v>1309.15</v>
+        <v>1309.17</v>
       </c>
       <c r="D112" s="18" t="n">
         <v>15.3273</v>
@@ -50151,7 +50151,7 @@
         </is>
       </c>
       <c r="C114" s="17" t="n">
-        <v>1315.81</v>
+        <v>1315.78</v>
       </c>
       <c r="D114" s="18" t="n">
         <v>16.9863</v>
@@ -50183,7 +50183,7 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1613.72</v>
+        <v>1613.75</v>
       </c>
       <c r="D115" s="18" t="n">
         <v>19.7214</v>
@@ -50247,7 +50247,7 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>1528.21</v>
+        <v>1528.2</v>
       </c>
       <c r="D117" s="18" t="n">
         <v>15.44</v>
@@ -50279,7 +50279,7 @@
         </is>
       </c>
       <c r="C118" s="17" t="n">
-        <v>1556.72</v>
+        <v>1556.7</v>
       </c>
       <c r="D118" s="18" t="n">
         <v>20.5448</v>
@@ -50311,7 +50311,7 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>1207.75</v>
+        <v>1207.76</v>
       </c>
       <c r="D119" s="18" t="n">
         <v>10.0609</v>
@@ -50343,7 +50343,7 @@
         </is>
       </c>
       <c r="C120" s="17" t="n">
-        <v>1643.82</v>
+        <v>1643.8</v>
       </c>
       <c r="D120" s="18" t="n">
         <v>19.3999</v>
@@ -50375,7 +50375,7 @@
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1119.26</v>
+        <v>1119.25</v>
       </c>
       <c r="D121" s="18" t="n">
         <v>23.6589</v>
@@ -50439,7 +50439,7 @@
         </is>
       </c>
       <c r="C123" s="17" t="n">
-        <v>1611.35</v>
+        <v>1611.34</v>
       </c>
       <c r="D123" s="18" t="n">
         <v>29.0269</v>
@@ -50548,7 +50548,7 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>4315.37</v>
+        <v>4315.35</v>
       </c>
       <c r="C5" s="19">
         <f>ROUND(SUMIFS(Mese!$Q$5:$Q$254,Mese!$B$5:$B$254,A5),2)</f>
@@ -50559,7 +50559,7 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>3049.18</v>
+        <v>3049.26</v>
       </c>
       <c r="F5" s="19">
         <f>ROUND(SUMIFS(Mese!$O$5:$O$254,Mese!$B$5:$B$254,A5),2)</f>
@@ -50581,7 +50581,7 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>17977.09</v>
+        <v>17977</v>
       </c>
       <c r="C6" s="19">
         <f>ROUND(SUMIFS(Mese!$Q$5:$Q$254,Mese!$B$5:$B$254,A6),2)</f>
@@ -50592,7 +50592,7 @@
         <v/>
       </c>
       <c r="E6" s="17" t="n">
-        <v>12763.7</v>
+        <v>12763.85</v>
       </c>
       <c r="F6" s="19">
         <f>ROUND(SUMIFS(Mese!$O$5:$O$254,Mese!$B$5:$B$254,A6),2)</f>
@@ -50614,7 +50614,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>6045.78</v>
+        <v>6045.7</v>
       </c>
       <c r="C7" s="19">
         <f>ROUND(SUMIFS(Mese!$Q$5:$Q$254,Mese!$B$5:$B$254,A7),2)</f>
@@ -50625,7 +50625,7 @@
         <v/>
       </c>
       <c r="E7" s="17" t="n">
-        <v>4462.18</v>
+        <v>4462.36</v>
       </c>
       <c r="F7" s="19">
         <f>ROUND(SUMIFS(Mese!$O$5:$O$254,Mese!$B$5:$B$254,A7),2)</f>

--- a/deliverables/foglio_controllo_cedolini.xlsx
+++ b/deliverables/foglio_controllo_cedolini.xlsx
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="E14" s="31">
         <f>Mese!X11</f>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D20" s="30" t="n">
-        <v>1970.29</v>
+        <v>1970.28</v>
       </c>
       <c r="E20" s="31">
         <f>Mese!AG11</f>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="D28" s="30" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="E28" s="31">
         <f>Mese!X23</f>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="D34" s="30" t="n">
-        <v>1752.09</v>
+        <v>1752.08</v>
       </c>
       <c r="E34" s="31">
         <f>Mese!AG23</f>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D63" s="30" t="n">
-        <v>2723.45</v>
+        <v>2984.22</v>
       </c>
       <c r="E63" s="31">
         <f>Mese!X53</f>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="D66" s="30" t="n">
-        <v>257.32</v>
+        <v>281.31</v>
       </c>
       <c r="E66" s="31">
         <f>Mese!AB53</f>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D67" s="30" t="n">
-        <v>241.96</v>
+        <v>264.5</v>
       </c>
       <c r="E67" s="31">
         <f>Mese!AC53</f>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="D69" s="30" t="n">
-        <v>2009.89</v>
+        <v>2155.51</v>
       </c>
       <c r="E69" s="31">
         <f>Mese!AG53</f>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="D126" s="30" t="n">
-        <v>1675.2</v>
+        <v>1675.19</v>
       </c>
       <c r="E126" s="31">
         <f>Mese!X107</f>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="D132" s="30" t="n">
-        <v>1347.19</v>
+        <v>1347.18</v>
       </c>
       <c r="E132" s="31">
         <f>Mese!AG107</f>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="D325" s="30" t="n">
-        <v>2558.81</v>
+        <v>2558.8</v>
       </c>
       <c r="E325" s="31">
         <f>'Novembre 2026'!J30</f>
@@ -10213,7 +10213,7 @@
         </is>
       </c>
       <c r="D337" s="30" t="n">
-        <v>2280.95</v>
+        <v>2280.93</v>
       </c>
       <c r="E337" s="31">
         <f>'Novembre 2026'!J45</f>
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D357" s="30" t="n">
-        <v>2280.95</v>
+        <v>2280.93</v>
       </c>
       <c r="E357" s="31">
         <f>'Novembre 2026'!J70</f>
@@ -12832,7 +12832,7 @@
         </is>
       </c>
       <c r="D434" s="30" t="n">
-        <v>2492.17</v>
+        <v>2492.16</v>
       </c>
       <c r="E434" s="31">
         <f>Riepilogo!D20</f>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="D435" s="30" t="n">
-        <v>869.9400000000001</v>
+        <v>869.9299999999999</v>
       </c>
       <c r="E435" s="31">
         <f>Riepilogo!E20</f>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="D438" s="30" t="n">
-        <v>303.62</v>
+        <v>303.61</v>
       </c>
       <c r="E438" s="31">
         <f>Riepilogo!E21</f>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="D440" s="30" t="n">
-        <v>1594.74</v>
+        <v>1594.73</v>
       </c>
       <c r="E440" s="31">
         <f>Riepilogo!D22</f>
@@ -14929,7 +14929,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>1</v>
@@ -14944,13 +14944,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="17" t="n">
-        <v>2728.91</v>
+        <v>2728.9</v>
       </c>
       <c r="O11" s="17" t="n">
         <v>250.8</v>
       </c>
       <c r="P11" s="17" t="n">
-        <v>2478.11</v>
+        <v>2478.1</v>
       </c>
       <c r="Q11" s="17" t="n">
         <v>470.65</v>
@@ -14959,7 +14959,7 @@
         <v>37.17</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>1970.29</v>
+        <v>1970.28</v>
       </c>
       <c r="T11" s="17" t="n">
         <v>235.83</v>
@@ -16957,7 +16957,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>6</v>
@@ -16972,22 +16972,22 @@
         <v>0</v>
       </c>
       <c r="N23" s="17" t="n">
-        <v>2370.58</v>
+        <v>2370.56</v>
       </c>
       <c r="O23" s="17" t="n">
         <v>217.89</v>
       </c>
       <c r="P23" s="17" t="n">
-        <v>2152.69</v>
+        <v>2152.67</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>368.31</v>
+        <v>368.3</v>
       </c>
       <c r="R23" s="17" t="n">
         <v>32.29</v>
       </c>
       <c r="S23" s="17" t="n">
-        <v>1752.09</v>
+        <v>1752.08</v>
       </c>
       <c r="T23" s="17" t="n">
         <v>204.86</v>
@@ -17126,7 +17126,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>9</v>
@@ -17141,13 +17141,13 @@
         <v>0</v>
       </c>
       <c r="N24" s="17" t="n">
-        <v>2727.63</v>
+        <v>2727.62</v>
       </c>
       <c r="O24" s="17" t="n">
         <v>250.7</v>
       </c>
       <c r="P24" s="17" t="n">
-        <v>2476.93</v>
+        <v>2476.92</v>
       </c>
       <c r="Q24" s="17" t="n">
         <v>470.21</v>
@@ -17156,7 +17156,7 @@
         <v>37.15</v>
       </c>
       <c r="S24" s="17" t="n">
-        <v>1969.57</v>
+        <v>1969.56</v>
       </c>
       <c r="T24" s="17" t="n">
         <v>235.72</v>
@@ -17637,7 +17637,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>6</v>
@@ -17652,13 +17652,13 @@
         <v>0</v>
       </c>
       <c r="N27" s="17" t="n">
-        <v>2490.58</v>
+        <v>2490.56</v>
       </c>
       <c r="O27" s="17" t="n">
         <v>228.92</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>2261.66</v>
+        <v>2261.64</v>
       </c>
       <c r="Q27" s="17" t="n">
         <v>397.73</v>
@@ -17667,10 +17667,10 @@
         <v>33.92</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>1830.01</v>
+        <v>1829.99</v>
       </c>
       <c r="T27" s="17" t="n">
-        <v>215.24</v>
+        <v>215.23</v>
       </c>
       <c r="U27" s="18" t="n">
         <v>2.1667</v>
@@ -18144,7 +18144,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>3</v>
@@ -18159,13 +18159,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="17" t="n">
-        <v>2628.59</v>
+        <v>2628.58</v>
       </c>
       <c r="O30" s="17" t="n">
         <v>241.61</v>
       </c>
       <c r="P30" s="17" t="n">
-        <v>2386.98</v>
+        <v>2386.97</v>
       </c>
       <c r="Q30" s="17" t="n">
         <v>436.93</v>
@@ -18174,7 +18174,7 @@
         <v>35.8</v>
       </c>
       <c r="S30" s="17" t="n">
-        <v>1914.25</v>
+        <v>1914.24</v>
       </c>
       <c r="T30" s="17" t="n">
         <v>227.16</v>
@@ -20679,7 +20679,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="J45" s="15" t="n">
         <v>6</v>
@@ -20694,13 +20694,13 @@
         <v>0</v>
       </c>
       <c r="N45" s="17" t="n">
-        <v>2670.58</v>
+        <v>2670.56</v>
       </c>
       <c r="O45" s="17" t="n">
         <v>245.46</v>
       </c>
       <c r="P45" s="17" t="n">
-        <v>2425.12</v>
+        <v>2425.1</v>
       </c>
       <c r="Q45" s="17" t="n">
         <v>451.04</v>
@@ -20709,7 +20709,7 @@
         <v>36.38</v>
       </c>
       <c r="S45" s="17" t="n">
-        <v>1937.7</v>
+        <v>1937.68</v>
       </c>
       <c r="T45" s="17" t="n">
         <v>230.79</v>
@@ -21186,7 +21186,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>2186.25</v>
+        <v>2186.23</v>
       </c>
       <c r="J48" s="15" t="n">
         <v>4</v>
@@ -21201,22 +21201,22 @@
         <v>0</v>
       </c>
       <c r="N48" s="17" t="n">
-        <v>2577.57</v>
+        <v>2577.55</v>
       </c>
       <c r="O48" s="17" t="n">
         <v>236.92</v>
       </c>
       <c r="P48" s="17" t="n">
-        <v>2340.65</v>
+        <v>2340.63</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>419.79</v>
+        <v>419.78</v>
       </c>
       <c r="R48" s="17" t="n">
         <v>35.11</v>
       </c>
       <c r="S48" s="17" t="n">
-        <v>1885.75</v>
+        <v>1885.74</v>
       </c>
       <c r="T48" s="17" t="n">
         <v>222.75</v>
@@ -21693,7 +21693,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="J51" s="15" t="n">
         <v>0</v>
@@ -21708,13 +21708,13 @@
         <v>0</v>
       </c>
       <c r="N51" s="17" t="n">
-        <v>2584.07</v>
+        <v>2584.06</v>
       </c>
       <c r="O51" s="17" t="n">
         <v>237.47</v>
       </c>
       <c r="P51" s="17" t="n">
-        <v>2346.6</v>
+        <v>2346.59</v>
       </c>
       <c r="Q51" s="17" t="n">
         <v>421.99</v>
@@ -21723,7 +21723,7 @@
         <v>35.2</v>
       </c>
       <c r="S51" s="17" t="n">
-        <v>1889.41</v>
+        <v>1889.4</v>
       </c>
       <c r="T51" s="17" t="n">
         <v>223.31</v>
@@ -22031,7 +22031,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>2723.45</v>
+        <v>2984.22</v>
       </c>
       <c r="J53" s="15" t="n">
         <v>3</v>
@@ -22046,25 +22046,25 @@
         <v>0</v>
       </c>
       <c r="N53" s="17" t="n">
-        <v>2799.83</v>
+        <v>3060.6</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>257.32</v>
+        <v>281.31</v>
       </c>
       <c r="P53" s="17" t="n">
-        <v>2542.51</v>
+        <v>2779.29</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>494.48</v>
+        <v>582.09</v>
       </c>
       <c r="R53" s="17" t="n">
-        <v>38.14</v>
+        <v>41.69</v>
       </c>
       <c r="S53" s="17" t="n">
-        <v>2009.89</v>
+        <v>2155.51</v>
       </c>
       <c r="T53" s="17" t="n">
-        <v>241.96</v>
+        <v>264.5</v>
       </c>
       <c r="U53" s="18" t="n">
         <v>2.1667</v>
@@ -24908,7 +24908,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="J70" s="15" t="n">
         <v>2</v>
@@ -24923,13 +24923,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="17" t="n">
-        <v>2279.26</v>
+        <v>2279.24</v>
       </c>
       <c r="O70" s="17" t="n">
         <v>209.44</v>
       </c>
       <c r="P70" s="17" t="n">
-        <v>2069.82</v>
+        <v>2069.8</v>
       </c>
       <c r="Q70" s="17" t="n">
         <v>345.93</v>
@@ -24938,7 +24938,7 @@
         <v>31.05</v>
       </c>
       <c r="S70" s="17" t="n">
-        <v>1692.84</v>
+        <v>1692.82</v>
       </c>
       <c r="T70" s="17" t="n">
         <v>196.97</v>
@@ -26940,7 +26940,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>1</v>
@@ -26955,13 +26955,13 @@
         <v>0</v>
       </c>
       <c r="N82" s="17" t="n">
-        <v>2728.91</v>
+        <v>2728.9</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>250.8</v>
       </c>
       <c r="P82" s="17" t="n">
-        <v>2478.11</v>
+        <v>2478.1</v>
       </c>
       <c r="Q82" s="17" t="n">
         <v>470.65</v>
@@ -26970,7 +26970,7 @@
         <v>37.17</v>
       </c>
       <c r="S82" s="17" t="n">
-        <v>1970.29</v>
+        <v>1970.28</v>
       </c>
       <c r="T82" s="17" t="n">
         <v>235.83</v>
@@ -28968,7 +28968,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="J94" s="15" t="n">
         <v>7</v>
@@ -28983,22 +28983,22 @@
         <v>1059.83</v>
       </c>
       <c r="N94" s="17" t="n">
-        <v>3453.24</v>
+        <v>3453.22</v>
       </c>
       <c r="O94" s="17" t="n">
         <v>317.33</v>
       </c>
       <c r="P94" s="17" t="n">
-        <v>3135.91</v>
+        <v>3135.89</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>714.04</v>
+        <v>714.03</v>
       </c>
       <c r="R94" s="17" t="n">
         <v>47.04</v>
       </c>
       <c r="S94" s="17" t="n">
-        <v>2374.83</v>
+        <v>2374.82</v>
       </c>
       <c r="T94" s="17" t="n">
         <v>206.84</v>
@@ -31165,7 +31165,7 @@
         <v>1</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>1675.2</v>
+        <v>1675.19</v>
       </c>
       <c r="J107" s="15" t="n">
         <v>2</v>
@@ -31180,13 +31180,13 @@
         <v>0</v>
       </c>
       <c r="N107" s="17" t="n">
-        <v>1746.95</v>
+        <v>1746.94</v>
       </c>
       <c r="O107" s="17" t="n">
         <v>160.55</v>
       </c>
       <c r="P107" s="17" t="n">
-        <v>1586.4</v>
+        <v>1586.39</v>
       </c>
       <c r="Q107" s="17" t="n">
         <v>215.41</v>
@@ -31195,7 +31195,7 @@
         <v>23.8</v>
       </c>
       <c r="S107" s="17" t="n">
-        <v>1347.19</v>
+        <v>1347.18</v>
       </c>
       <c r="T107" s="17" t="n">
         <v>150.97</v>
@@ -31503,7 +31503,7 @@
         <v>1</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>2723.45</v>
+        <v>2984.22</v>
       </c>
       <c r="J109" s="15" t="n">
         <v>1</v>
@@ -31518,25 +31518,25 @@
         <v>0</v>
       </c>
       <c r="N109" s="17" t="n">
-        <v>3048.91</v>
+        <v>3309.68</v>
       </c>
       <c r="O109" s="17" t="n">
-        <v>280.2</v>
+        <v>304.19</v>
       </c>
       <c r="P109" s="17" t="n">
-        <v>2768.71</v>
+        <v>3005.49</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>578.17</v>
+        <v>665.78</v>
       </c>
       <c r="R109" s="17" t="n">
-        <v>41.53</v>
+        <v>45.08</v>
       </c>
       <c r="S109" s="17" t="n">
-        <v>2149.01</v>
+        <v>2294.63</v>
       </c>
       <c r="T109" s="17" t="n">
-        <v>263.49</v>
+        <v>286.02</v>
       </c>
       <c r="U109" s="18" t="n">
         <v>2.1667</v>
@@ -46855,7 +46855,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>1970.29</v>
+        <v>1970.28</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>17.3519</v>
@@ -47239,7 +47239,7 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1752.09</v>
+        <v>1752.08</v>
       </c>
       <c r="D23" s="18" t="n">
         <v>20.113</v>
@@ -47271,7 +47271,7 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>1969.57</v>
+        <v>1969.56</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>7.9673</v>
@@ -47367,7 +47367,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1830.01</v>
+        <v>1829.99</v>
       </c>
       <c r="D27" s="18" t="n">
         <v>20.5321</v>
@@ -47463,7 +47463,7 @@
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1914.25</v>
+        <v>1914.24</v>
       </c>
       <c r="D30" s="18" t="n">
         <v>17.7804</v>
@@ -47943,7 +47943,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>1937.7</v>
+        <v>1937.68</v>
       </c>
       <c r="D45" s="18" t="n">
         <v>9.230600000000001</v>
@@ -48039,7 +48039,7 @@
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1899.48</v>
+        <v>1899.47</v>
       </c>
       <c r="D48" s="18" t="n">
         <v>4.6458</v>
@@ -48135,7 +48135,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1889.41</v>
+        <v>1889.4</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>5.2692</v>
@@ -48199,7 +48199,7 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>2009.89</v>
+        <v>2155.51</v>
       </c>
       <c r="D53" s="18" t="n">
         <v>11.5295</v>
@@ -48743,7 +48743,7 @@
         </is>
       </c>
       <c r="C70" s="17" t="n">
-        <v>1692.84</v>
+        <v>1692.82</v>
       </c>
       <c r="D70" s="18" t="n">
         <v>9.1441</v>
@@ -49127,7 +49127,7 @@
         </is>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1970.29</v>
+        <v>1970.28</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>12.1962</v>
@@ -49511,7 +49511,7 @@
         </is>
       </c>
       <c r="C94" s="17" t="n">
-        <v>1752.09</v>
+        <v>1752.08</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>5.922</v>
@@ -49991,7 +49991,7 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>2149.01</v>
+        <v>2294.63</v>
       </c>
       <c r="D109" s="18" t="n">
         <v>21.9779</v>
@@ -50581,7 +50581,7 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>17977</v>
+        <v>18064.58</v>
       </c>
       <c r="C6" s="19">
         <f>ROUND(SUMIFS(Mese!$Q$5:$Q$254,Mese!$B$5:$B$254,A6),2)</f>
@@ -50592,7 +50592,7 @@
         <v/>
       </c>
       <c r="E6" s="17" t="n">
-        <v>12763.85</v>
+        <v>12787.84</v>
       </c>
       <c r="F6" s="19">
         <f>ROUND(SUMIFS(Mese!$O$5:$O$254,Mese!$B$5:$B$254,A6),2)</f>
@@ -50614,7 +50614,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>6045.7</v>
+        <v>6133.31</v>
       </c>
       <c r="C7" s="19">
         <f>ROUND(SUMIFS(Mese!$Q$5:$Q$254,Mese!$B$5:$B$254,A7),2)</f>
@@ -50625,7 +50625,7 @@
         <v/>
       </c>
       <c r="E7" s="17" t="n">
-        <v>4462.36</v>
+        <v>4486.35</v>
       </c>
       <c r="F7" s="19">
         <f>ROUND(SUMIFS(Mese!$O$5:$O$254,Mese!$B$5:$B$254,A7),2)</f>
@@ -62344,22 +62344,22 @@
         <v>2183.09</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>540.36</v>
+        <v>540.37</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0</v>
+        <v>260.76</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>2662.68</v>
+        <v>2923.46</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>2723.45</v>
+        <v>2984.22</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>2784.22</v>
+        <v>3044.98</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>2853.66</v>
+        <v>3114.42</v>
       </c>
       <c r="I5" s="17" t="n">
         <v>25.46</v>
@@ -62375,19 +62375,19 @@
         <v>1966.54</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>537.53</v>
+        <v>537.52</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>2449.33</v>
+        <v>2449.32</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>2504.07</v>
+        <v>2504.06</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>2558.81</v>
+        <v>2558.8</v>
       </c>
       <c r="H6" s="17" t="n">
         <v>2621.36</v>
@@ -62406,22 +62406,22 @@
         <v>1701.04</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>532.5599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>2186.25</v>
+        <v>2186.23</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>2233.6</v>
+        <v>2233.58</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>2280.95</v>
+        <v>2280.93</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>2335.06</v>
+        <v>2335.04</v>
       </c>
       <c r="I7" s="17" t="n">
         <v>22.83</v>
@@ -62545,7 +62545,7 @@
         <v>1568.09</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>1600.54</v>
+        <v>1600.53</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>19.73</v>
